--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -1327,45 +1327,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>Rotate</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>麻：逆时针旋转 value×90 度，不产生分数效果</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>SourRecipeMult</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>酸：未上菜时场上同菜谱食物倍率×value</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>SaltyRecipeGold</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>咸：未上菜时场上每个同菜谱食物+value金币</t>
         </is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="K45" s="0" t="inlineStr">
         <is>
-          <t>周围菜(共边相邻+对角相邻)</t>
+          <t>周围菜(仅共边相邻)</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb80830dca1154439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb752497e1e745e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2210,14 +2210,14 @@
       <x:c r="F65"/>
       <x:c r="G65"/>
       <x:c r="H65" t="str">
-        <x:v>TransferScore</x:v>
+        <x:v>TransferSkills</x:v>
       </x:c>
       <x:c r="I65"/>
       <x:c r="J65" t="str">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>来源加法分按比例转移给目标</x:v>
+        <x:v>来源技能传递给目标</x:v>
       </x:c>
       <x:c r="L65"/>
     </x:row>
@@ -2230,14 +2230,14 @@
       <x:c r="F66"/>
       <x:c r="G66"/>
       <x:c r="H66" t="str">
-        <x:v>ExtraSettlement</x:v>
+        <x:v>AddLayer</x:v>
       </x:c>
       <x:c r="I66"/>
       <x:c r="J66" t="str">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>目标额外结算X次</x:v>
+        <x:v>层数+X(mult时*X)</x:v>
       </x:c>
       <x:c r="L66"/>
     </x:row>
@@ -2250,14 +2250,14 @@
       <x:c r="F67"/>
       <x:c r="G67"/>
       <x:c r="H67" t="str">
-        <x:v>TransferSkills</x:v>
+        <x:v>ConsumeLayer</x:v>
       </x:c>
       <x:c r="I67"/>
       <x:c r="J67" t="str">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>来源技能传递给目标</x:v>
+        <x:v>层数-X</x:v>
       </x:c>
       <x:c r="L67"/>
     </x:row>
@@ -2270,14 +2270,14 @@
       <x:c r="F68"/>
       <x:c r="G68"/>
       <x:c r="H68" t="str">
-        <x:v>AddLayer</x:v>
+        <x:v>GrantGold</x:v>
       </x:c>
       <x:c r="I68"/>
       <x:c r="J68" t="str">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>层数+X(mult时*X)</x:v>
+        <x:v>获得X*count金币</x:v>
       </x:c>
       <x:c r="L68"/>
     </x:row>
@@ -2290,14 +2290,14 @@
       <x:c r="F69"/>
       <x:c r="G69"/>
       <x:c r="H69" t="str">
-        <x:v>ConsumeLayer</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I69"/>
       <x:c r="J69" t="str">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>层数-X</x:v>
+        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
       </x:c>
       <x:c r="L69"/>
     </x:row>
@@ -2310,14 +2310,14 @@
       <x:c r="F70"/>
       <x:c r="G70"/>
       <x:c r="H70" t="str">
-        <x:v>GrantGold</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I70"/>
       <x:c r="J70" t="str">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>获得X*count金币</x:v>
+        <x:v>目标永久加法+X(跨结算持久)</x:v>
       </x:c>
       <x:c r="L70"/>
     </x:row>
@@ -2330,14 +2330,14 @@
       <x:c r="F71"/>
       <x:c r="G71"/>
       <x:c r="H71" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>AddCountAs</x:v>
       </x:c>
       <x:c r="I71"/>
       <x:c r="J71" t="str">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
+        <x:v>目标"视为食物数"+X*count</x:v>
       </x:c>
       <x:c r="L71"/>
     </x:row>
@@ -2350,14 +2350,14 @@
       <x:c r="F72"/>
       <x:c r="G72"/>
       <x:c r="H72" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>CopySkill</x:v>
       </x:c>
       <x:c r="I72"/>
       <x:c r="J72" t="str">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>目标永久加法+X(跨结算持久)</x:v>
+        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
       </x:c>
       <x:c r="L72"/>
     </x:row>
@@ -2370,14 +2370,14 @@
       <x:c r="F73"/>
       <x:c r="G73"/>
       <x:c r="H73" t="str">
-        <x:v>PermanentAddMult</x:v>
+        <x:v>TriggerSweetTransfer</x:v>
       </x:c>
       <x:c r="I73"/>
       <x:c r="J73" t="str">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>目标永久乘区*X(跨结算持久)</x:v>
+        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
       </x:c>
       <x:c r="L73"/>
     </x:row>
@@ -2390,34 +2390,42 @@
       <x:c r="F74"/>
       <x:c r="G74"/>
       <x:c r="H74" t="str">
-        <x:v>AddCountAs</x:v>
+        <x:v>ExtraSweetTransfer</x:v>
       </x:c>
       <x:c r="I74"/>
       <x:c r="J74" t="str">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>目标"视为食物数"+X*count</x:v>
+        <x:v>目标每次甜蜜传递额外触发X次（隐藏、可叠加、每次重新随机目标）</x:v>
       </x:c>
       <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75"/>
-      <x:c r="B75"/>
-      <x:c r="C75"/>
-      <x:c r="D75"/>
+      <x:c r="B75" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E75"/>
-      <x:c r="F75"/>
+      <x:c r="F75" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>CopySkill</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
@@ -2430,34 +2438,42 @@
       <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>TempCopyDish</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>临时复制目标菜到空格(本次品鉴)</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77"/>
-      <x:c r="B77"/>
-      <x:c r="C77"/>
-      <x:c r="D77"/>
+      <x:c r="B77" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E77"/>
-      <x:c r="F77"/>
+      <x:c r="F77" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>TriggerSweetTransfer</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I77"/>
-      <x:c r="J77" t="str">
-        <x:v>15</x:v>
+      <x:c r="J77" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
@@ -2470,42 +2486,34 @@
       <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>ExtraSweetTransfer</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I78"/>
-      <x:c r="J78" t="str">
-        <x:v>16</x:v>
+      <x:c r="J78" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>目标每次甜蜜传递额外触发X次（隐藏、可叠加、每次重新随机目标）</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79"/>
-      <x:c r="B79" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C79" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D79" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
       <x:c r="E79"/>
-      <x:c r="F79" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I79"/>
-      <x:c r="J79" t="str">
-        <x:v>0</x:v>
+      <x:c r="J79" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>结算时</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
@@ -2518,42 +2526,34 @@
       <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I80"/>
-      <x:c r="J80" t="str">
-        <x:v>1</x:v>
+      <x:c r="J80" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81"/>
-      <x:c r="B81" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C81" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D81" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
       <x:c r="E81"/>
-      <x:c r="F81" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>None</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>无</x:v>
+        <x:v>倍率×值(黑曜石)</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
@@ -2566,14 +2566,14 @@
       <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>AddMultFlatPerCell</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,14 +2586,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>GrantGoldIfCellCount</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2606,14 +2606,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>GrantItemRollIfCellCount</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2625,16 +2625,10 @@
       <x:c r="E85"/>
       <x:c r="F85"/>
       <x:c r="G85"/>
-      <x:c r="H85" t="str">
-        <x:v>AddMult</x:v>
-      </x:c>
+      <x:c r="H85"/>
       <x:c r="I85"/>
-      <x:c r="J85" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K85" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
-      </x:c>
+      <x:c r="J85"/>
+      <x:c r="K85"/>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">
@@ -2645,16 +2639,10 @@
       <x:c r="E86"/>
       <x:c r="F86"/>
       <x:c r="G86"/>
-      <x:c r="H86" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
-      </x:c>
+      <x:c r="H86"/>
       <x:c r="I86"/>
-      <x:c r="J86" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K86" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
-      </x:c>
+      <x:c r="J86"/>
+      <x:c r="K86"/>
       <x:c r="L86"/>
     </x:row>
     <x:row r="87">
@@ -2665,16 +2653,10 @@
       <x:c r="E87"/>
       <x:c r="F87"/>
       <x:c r="G87"/>
-      <x:c r="H87" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
-      </x:c>
+      <x:c r="H87"/>
       <x:c r="I87"/>
-      <x:c r="J87" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K87" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
-      </x:c>
+      <x:c r="J87"/>
+      <x:c r="K87"/>
       <x:c r="L87"/>
     </x:row>
     <x:row r="88">
@@ -2685,16 +2667,10 @@
       <x:c r="E88"/>
       <x:c r="F88"/>
       <x:c r="G88"/>
-      <x:c r="H88" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
-      </x:c>
+      <x:c r="H88"/>
       <x:c r="I88"/>
-      <x:c r="J88" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K88" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
-      </x:c>
+      <x:c r="J88"/>
+      <x:c r="K88"/>
       <x:c r="L88"/>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb752497e1e745e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R190b6ce6e52b4f99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2403,97 +2403,97 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75"/>
-      <x:c r="B75" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C75" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D75" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
       <x:c r="E75"/>
-      <x:c r="F75" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F75"/>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>AddCurrentMult</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>结算时</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76"/>
-      <x:c r="B76"/>
-      <x:c r="C76"/>
-      <x:c r="D76"/>
+      <x:c r="B76" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E76"/>
-      <x:c r="F76"/>
+      <x:c r="F76" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77"/>
-      <x:c r="B77" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C77" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D77" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
       <x:c r="E77"/>
-      <x:c r="F77" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>None</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I77"/>
-      <x:c r="J77" t="n">
-        <x:v>0</x:v>
+      <x:c r="J77" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>无</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78"/>
-      <x:c r="B78"/>
-      <x:c r="C78"/>
-      <x:c r="D78"/>
+      <x:c r="B78" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E78"/>
-      <x:c r="F78"/>
+      <x:c r="F78" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2506,14 +2506,14 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I79"/>
       <x:c r="J79" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
@@ -2526,14 +2526,14 @@
       <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I80"/>
       <x:c r="J80" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2546,14 +2546,14 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
@@ -2566,14 +2566,14 @@
       <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>倍率×值(黑曜石)</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,14 +2586,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>AddMultFlatPerCell</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2606,14 +2606,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
+        <x:v>GrantGoldIfCellCount</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2625,10 +2625,16 @@
       <x:c r="E85"/>
       <x:c r="F85"/>
       <x:c r="G85"/>
-      <x:c r="H85"/>
+      <x:c r="H85" t="str">
+        <x:v>GrantItemRollIfCellCount</x:v>
+      </x:c>
       <x:c r="I85"/>
-      <x:c r="J85"/>
-      <x:c r="K85"/>
+      <x:c r="J85" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+      </x:c>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R190b6ce6e52b4f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b706647d814cd0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2390,110 +2390,110 @@
       <x:c r="F74"/>
       <x:c r="G74"/>
       <x:c r="H74" t="str">
-        <x:v>ExtraSweetTransfer</x:v>
+        <x:v>AddCurrentMult</x:v>
       </x:c>
       <x:c r="I74"/>
       <x:c r="J74" t="str">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>目标每次甜蜜传递额外触发X次（隐藏、可叠加、每次重新随机目标）</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
       </x:c>
       <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75"/>
-      <x:c r="B75"/>
-      <x:c r="C75"/>
-      <x:c r="D75"/>
+      <x:c r="B75" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E75"/>
-      <x:c r="F75"/>
+      <x:c r="F75" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>AddCurrentMult</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76"/>
-      <x:c r="B76" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C76" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D76" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
       <x:c r="E76"/>
-      <x:c r="F76" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>结算时</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77"/>
-      <x:c r="B77"/>
-      <x:c r="C77"/>
-      <x:c r="D77"/>
+      <x:c r="B77" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E77"/>
-      <x:c r="F77"/>
+      <x:c r="F77" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I77"/>
-      <x:c r="J77" t="str">
-        <x:v>1</x:v>
+      <x:c r="J77" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78"/>
-      <x:c r="B78" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C78" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D78" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
       <x:c r="E78"/>
-      <x:c r="F78" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>None</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>无</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2506,14 +2506,14 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I79"/>
       <x:c r="J79" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
@@ -2526,14 +2526,14 @@
       <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I80"/>
       <x:c r="J80" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2546,14 +2546,14 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>倍率×值(黑曜石)</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
@@ -2566,14 +2566,14 @@
       <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>AddMultFlatPerCell</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,14 +2586,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>GrantGoldIfCellCount</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2606,14 +2606,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>GrantItemRollIfCellCount</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2625,16 +2625,10 @@
       <x:c r="E85"/>
       <x:c r="F85"/>
       <x:c r="G85"/>
-      <x:c r="H85" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
-      </x:c>
+      <x:c r="H85"/>
       <x:c r="I85"/>
-      <x:c r="J85" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K85" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
-      </x:c>
+      <x:c r="J85"/>
+      <x:c r="K85"/>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2403,97 +2403,97 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75"/>
-      <x:c r="B75" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C75" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D75" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
       <x:c r="E75"/>
-      <x:c r="F75" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F75"/>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>AddCurrentScore</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>结算时</x:v>
+        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76"/>
-      <x:c r="B76"/>
-      <x:c r="C76"/>
-      <x:c r="D76"/>
+      <x:c r="B76" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E76"/>
-      <x:c r="F76"/>
+      <x:c r="F76" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77"/>
-      <x:c r="B77" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C77" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D77" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
       <x:c r="E77"/>
-      <x:c r="F77" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>None</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I77"/>
-      <x:c r="J77" t="n">
-        <x:v>0</x:v>
+      <x:c r="J77" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>无</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78"/>
-      <x:c r="B78"/>
-      <x:c r="C78"/>
-      <x:c r="D78"/>
+      <x:c r="B78" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E78"/>
-      <x:c r="F78"/>
+      <x:c r="F78" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2506,14 +2506,14 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I79"/>
       <x:c r="J79" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
@@ -2526,14 +2526,14 @@
       <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I80"/>
       <x:c r="J80" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2546,14 +2546,14 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
@@ -2566,14 +2566,14 @@
       <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>倍率×值(黑曜石)</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,14 +2586,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>AddMultFlatPerCell</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2606,14 +2606,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
+        <x:v>GrantGoldIfCellCount</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2625,10 +2625,16 @@
       <x:c r="E85"/>
       <x:c r="F85"/>
       <x:c r="G85"/>
-      <x:c r="H85"/>
+      <x:c r="H85" t="str">
+        <x:v>GrantItemRollIfCellCount</x:v>
+      </x:c>
       <x:c r="I85"/>
-      <x:c r="J85"/>
-      <x:c r="K85"/>
+      <x:c r="J85" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+      </x:c>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">
@@ -2673,6 +2679,20 @@
       <x:c r="K88"/>
       <x:c r="L88"/>
     </x:row>
+    <x:row r="89">
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
+      <x:c r="J89"/>
+      <x:c r="K89"/>
+      <x:c r="L89"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b706647d814cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad7cb71ccf844c7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1891,29 +1891,21 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51"/>
-      <x:c r="B51" t="str">
-        <x:v>CompareOp</x:v>
-      </x:c>
-      <x:c r="C51" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D51" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
       <x:c r="E51"/>
-      <x:c r="F51" t="str">
-        <x:v>比较符</x:v>
-      </x:c>
+      <x:c r="F51"/>
       <x:c r="G51"/>
       <x:c r="H51" t="str">
-        <x:v>None</x:v>
+        <x:v>Left</x:v>
       </x:c>
       <x:c r="I51"/>
       <x:c r="J51" t="str">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>不比较</x:v>
+        <x:v>本菜左侧（逐行取本菜最左占格左边的存在格）</x:v>
       </x:c>
       <x:c r="L51"/>
     </x:row>
@@ -1926,14 +1918,14 @@
       <x:c r="F52"/>
       <x:c r="G52"/>
       <x:c r="H52" t="str">
-        <x:v>Gte</x:v>
+        <x:v>Up</x:v>
       </x:c>
       <x:c r="I52"/>
       <x:c r="J52" t="str">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>大于等于</x:v>
+        <x:v>本菜上侧（逐列取本菜最上占格上边的存在格）</x:v>
       </x:c>
       <x:c r="L52"/>
     </x:row>
@@ -1946,14 +1938,14 @@
       <x:c r="F53"/>
       <x:c r="G53"/>
       <x:c r="H53" t="str">
-        <x:v>Lte</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="I53"/>
       <x:c r="J53" t="str">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>小于等于</x:v>
+        <x:v>本菜右侧（逐行取本菜最右占格右边的存在格）</x:v>
       </x:c>
       <x:c r="L53"/>
     </x:row>
@@ -1966,34 +1958,42 @@
       <x:c r="F54"/>
       <x:c r="G54"/>
       <x:c r="H54" t="str">
-        <x:v>Eq</x:v>
+        <x:v>Down</x:v>
       </x:c>
       <x:c r="I54"/>
       <x:c r="J54" t="str">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>等于</x:v>
+        <x:v>本菜下侧（逐列取本菜最下占格下边的存在格）</x:v>
       </x:c>
       <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55"/>
-      <x:c r="B55"/>
-      <x:c r="C55"/>
-      <x:c r="D55"/>
+      <x:c r="B55" t="str">
+        <x:v>CompareOp</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E55"/>
-      <x:c r="F55"/>
+      <x:c r="F55" t="str">
+        <x:v>比较符</x:v>
+      </x:c>
       <x:c r="G55"/>
       <x:c r="H55" t="str">
-        <x:v>Gt</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I55"/>
       <x:c r="J55" t="str">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>大于</x:v>
+        <x:v>不比较</x:v>
       </x:c>
       <x:c r="L55"/>
     </x:row>
@@ -2006,42 +2006,34 @@
       <x:c r="F56"/>
       <x:c r="G56"/>
       <x:c r="H56" t="str">
-        <x:v>Lt</x:v>
+        <x:v>Gte</x:v>
       </x:c>
       <x:c r="I56"/>
       <x:c r="J56" t="str">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>小于</x:v>
+        <x:v>大于等于</x:v>
       </x:c>
       <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57"/>
-      <x:c r="B57" t="str">
-        <x:v>CountMode</x:v>
-      </x:c>
-      <x:c r="C57" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D57" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
       <x:c r="E57"/>
-      <x:c r="F57" t="str">
-        <x:v>计数模式</x:v>
-      </x:c>
+      <x:c r="F57"/>
       <x:c r="G57"/>
       <x:c r="H57" t="str">
-        <x:v>Per</x:v>
+        <x:v>Lte</x:v>
       </x:c>
       <x:c r="I57"/>
       <x:c r="J57" t="str">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>每有1个:count=raw</x:v>
+        <x:v>小于等于</x:v>
       </x:c>
       <x:c r="L57"/>
     </x:row>
@@ -2054,14 +2046,14 @@
       <x:c r="F58"/>
       <x:c r="G58"/>
       <x:c r="H58" t="str">
-        <x:v>Reach</x:v>
+        <x:v>Eq</x:v>
       </x:c>
       <x:c r="I58"/>
       <x:c r="J58" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>达到阈值:闸门</x:v>
+        <x:v>等于</x:v>
       </x:c>
       <x:c r="L58"/>
     </x:row>
@@ -2074,90 +2066,82 @@
       <x:c r="F59"/>
       <x:c r="G59"/>
       <x:c r="H59" t="str">
-        <x:v>Gate</x:v>
+        <x:v>Gt</x:v>
       </x:c>
       <x:c r="I59"/>
       <x:c r="J59" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>布尔条件:闸门</x:v>
+        <x:v>大于</x:v>
       </x:c>
       <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60"/>
-      <x:c r="B60" t="str">
-        <x:v>CountUnit</x:v>
-      </x:c>
-      <x:c r="C60" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D60" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
       <x:c r="E60"/>
-      <x:c r="F60" t="str">
-        <x:v>计数单位</x:v>
-      </x:c>
+      <x:c r="F60"/>
       <x:c r="G60"/>
       <x:c r="H60" t="str">
-        <x:v>Instances</x:v>
+        <x:v>Lt</x:v>
       </x:c>
       <x:c r="I60"/>
       <x:c r="J60" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>按实例(个)</x:v>
+        <x:v>小于</x:v>
       </x:c>
       <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61"/>
-      <x:c r="B61"/>
-      <x:c r="C61"/>
-      <x:c r="D61"/>
+      <x:c r="B61" t="str">
+        <x:v>CountMode</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E61"/>
-      <x:c r="F61"/>
+      <x:c r="F61" t="str">
+        <x:v>计数模式</x:v>
+      </x:c>
       <x:c r="G61"/>
       <x:c r="H61" t="str">
-        <x:v>Kinds</x:v>
+        <x:v>Per</x:v>
       </x:c>
       <x:c r="I61"/>
       <x:c r="J61" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>按BaseId去重(种)</x:v>
+        <x:v>每有1个:count=raw</x:v>
       </x:c>
       <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62"/>
-      <x:c r="B62" t="str">
-        <x:v>SkillActionType</x:v>
-      </x:c>
-      <x:c r="C62" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D62" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B62"/>
+      <x:c r="C62"/>
+      <x:c r="D62"/>
       <x:c r="E62"/>
-      <x:c r="F62" t="str">
-        <x:v>技能行为类型</x:v>
-      </x:c>
+      <x:c r="F62"/>
       <x:c r="G62"/>
       <x:c r="H62" t="str">
-        <x:v>None</x:v>
+        <x:v>Reach</x:v>
       </x:c>
       <x:c r="I62"/>
       <x:c r="J62" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>无行为</x:v>
+        <x:v>达到阈值:闸门</x:v>
       </x:c>
       <x:c r="L62"/>
     </x:row>
@@ -2170,34 +2154,42 @@
       <x:c r="F63"/>
       <x:c r="G63"/>
       <x:c r="H63" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>Gate</x:v>
       </x:c>
       <x:c r="I63"/>
       <x:c r="J63" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>目标加法区+X*count</x:v>
+        <x:v>布尔条件:闸门</x:v>
       </x:c>
       <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64"/>
-      <x:c r="B64"/>
-      <x:c r="C64"/>
-      <x:c r="D64"/>
+      <x:c r="B64" t="str">
+        <x:v>CountUnit</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E64"/>
-      <x:c r="F64"/>
+      <x:c r="F64" t="str">
+        <x:v>计数单位</x:v>
+      </x:c>
       <x:c r="G64"/>
       <x:c r="H64" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>Instances</x:v>
       </x:c>
       <x:c r="I64"/>
       <x:c r="J64" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>目标乘区*X(叠count次)</x:v>
+        <x:v>按实例(个)</x:v>
       </x:c>
       <x:c r="L64"/>
     </x:row>
@@ -2210,34 +2202,42 @@
       <x:c r="F65"/>
       <x:c r="G65"/>
       <x:c r="H65" t="str">
-        <x:v>TransferSkills</x:v>
+        <x:v>Kinds</x:v>
       </x:c>
       <x:c r="I65"/>
       <x:c r="J65" t="str">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>来源技能传递给目标</x:v>
+        <x:v>按BaseId去重(种)</x:v>
       </x:c>
       <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66"/>
-      <x:c r="B66"/>
-      <x:c r="C66"/>
-      <x:c r="D66"/>
+      <x:c r="B66" t="str">
+        <x:v>SkillActionType</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E66"/>
-      <x:c r="F66"/>
+      <x:c r="F66" t="str">
+        <x:v>技能行为类型</x:v>
+      </x:c>
       <x:c r="G66"/>
       <x:c r="H66" t="str">
-        <x:v>AddLayer</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I66"/>
       <x:c r="J66" t="str">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>层数+X(mult时*X)</x:v>
+        <x:v>无行为</x:v>
       </x:c>
       <x:c r="L66"/>
     </x:row>
@@ -2250,14 +2250,14 @@
       <x:c r="F67"/>
       <x:c r="G67"/>
       <x:c r="H67" t="str">
-        <x:v>ConsumeLayer</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I67"/>
       <x:c r="J67" t="str">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>层数-X</x:v>
+        <x:v>目标加法区+X*count</x:v>
       </x:c>
       <x:c r="L67"/>
     </x:row>
@@ -2270,14 +2270,14 @@
       <x:c r="F68"/>
       <x:c r="G68"/>
       <x:c r="H68" t="str">
-        <x:v>GrantGold</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I68"/>
       <x:c r="J68" t="str">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>获得X*count金币</x:v>
+        <x:v>目标乘区*X(叠count次)</x:v>
       </x:c>
       <x:c r="L68"/>
     </x:row>
@@ -2290,14 +2290,14 @@
       <x:c r="F69"/>
       <x:c r="G69"/>
       <x:c r="H69" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>TransferSkills</x:v>
       </x:c>
       <x:c r="I69"/>
       <x:c r="J69" t="str">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
+        <x:v>来源技能传递给目标</x:v>
       </x:c>
       <x:c r="L69"/>
     </x:row>
@@ -2310,14 +2310,14 @@
       <x:c r="F70"/>
       <x:c r="G70"/>
       <x:c r="H70" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddLayer</x:v>
       </x:c>
       <x:c r="I70"/>
       <x:c r="J70" t="str">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>目标永久加法+X(跨结算持久)</x:v>
+        <x:v>层数+X(mult时*X)</x:v>
       </x:c>
       <x:c r="L70"/>
     </x:row>
@@ -2330,14 +2330,14 @@
       <x:c r="F71"/>
       <x:c r="G71"/>
       <x:c r="H71" t="str">
-        <x:v>AddCountAs</x:v>
+        <x:v>ConsumeLayer</x:v>
       </x:c>
       <x:c r="I71"/>
       <x:c r="J71" t="str">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>目标"视为食物数"+X*count</x:v>
+        <x:v>层数-X</x:v>
       </x:c>
       <x:c r="L71"/>
     </x:row>
@@ -2350,14 +2350,14 @@
       <x:c r="F72"/>
       <x:c r="G72"/>
       <x:c r="H72" t="str">
-        <x:v>CopySkill</x:v>
+        <x:v>GrantGold</x:v>
       </x:c>
       <x:c r="I72"/>
       <x:c r="J72" t="str">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
+        <x:v>获得X*count金币</x:v>
       </x:c>
       <x:c r="L72"/>
     </x:row>
@@ -2370,14 +2370,14 @@
       <x:c r="F73"/>
       <x:c r="G73"/>
       <x:c r="H73" t="str">
-        <x:v>TriggerSweetTransfer</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I73"/>
       <x:c r="J73" t="str">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
+        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
       </x:c>
       <x:c r="L73"/>
     </x:row>
@@ -2390,14 +2390,14 @@
       <x:c r="F74"/>
       <x:c r="G74"/>
       <x:c r="H74" t="str">
-        <x:v>AddCurrentMult</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I74"/>
       <x:c r="J74" t="str">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
+        <x:v>目标永久加法+X(跨结算持久)</x:v>
       </x:c>
       <x:c r="L74"/>
     </x:row>
@@ -2410,42 +2410,34 @@
       <x:c r="F75"/>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>AddCurrentScore</x:v>
+        <x:v>AddCountAs</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
+        <x:v>目标"视为食物数"+X*count</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76"/>
-      <x:c r="B76" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C76" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D76" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
       <x:c r="E76"/>
-      <x:c r="F76" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>CopySkill</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>结算时</x:v>
+        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
@@ -2458,42 +2450,34 @@
       <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>TriggerSweetTransfer</x:v>
       </x:c>
       <x:c r="I77"/>
       <x:c r="J77" t="str">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78"/>
-      <x:c r="B78" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C78" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D78" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
       <x:c r="E78"/>
-      <x:c r="F78" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>None</x:v>
+        <x:v>AddCurrentMult</x:v>
       </x:c>
       <x:c r="I78"/>
-      <x:c r="J78" t="n">
-        <x:v>0</x:v>
+      <x:c r="J78" t="str">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>无</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2506,34 +2490,42 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>AddCurrentScore</x:v>
       </x:c>
       <x:c r="I79"/>
-      <x:c r="J79" t="n">
-        <x:v>1</x:v>
+      <x:c r="J79" t="str">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80"/>
-      <x:c r="B80"/>
-      <x:c r="C80"/>
-      <x:c r="D80"/>
+      <x:c r="B80" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E80"/>
-      <x:c r="F80"/>
+      <x:c r="F80" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I80"/>
-      <x:c r="J80" t="n">
-        <x:v>2</x:v>
+      <x:c r="J80" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2546,34 +2538,42 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I81"/>
-      <x:c r="J81" t="n">
-        <x:v>3</x:v>
+      <x:c r="J81" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82"/>
-      <x:c r="B82"/>
-      <x:c r="C82"/>
-      <x:c r="D82"/>
+      <x:c r="B82" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E82"/>
-      <x:c r="F82"/>
+      <x:c r="F82" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,14 +2586,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2606,14 +2606,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2626,14 +2626,14 @@
       <x:c r="F85"/>
       <x:c r="G85"/>
       <x:c r="H85" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I85"/>
       <x:c r="J85" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
@@ -2645,10 +2645,16 @@
       <x:c r="E86"/>
       <x:c r="F86"/>
       <x:c r="G86"/>
-      <x:c r="H86"/>
+      <x:c r="H86" t="str">
+        <x:v>AddMult</x:v>
+      </x:c>
       <x:c r="I86"/>
-      <x:c r="J86"/>
-      <x:c r="K86"/>
+      <x:c r="J86" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>倍率×值(黑曜石)</x:v>
+      </x:c>
       <x:c r="L86"/>
     </x:row>
     <x:row r="87">
@@ -2659,10 +2665,16 @@
       <x:c r="E87"/>
       <x:c r="F87"/>
       <x:c r="G87"/>
-      <x:c r="H87"/>
+      <x:c r="H87" t="str">
+        <x:v>AddMultFlatPerCell</x:v>
+      </x:c>
       <x:c r="I87"/>
-      <x:c r="J87"/>
-      <x:c r="K87"/>
+      <x:c r="J87" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+      </x:c>
       <x:c r="L87"/>
     </x:row>
     <x:row r="88">
@@ -2673,10 +2685,16 @@
       <x:c r="E88"/>
       <x:c r="F88"/>
       <x:c r="G88"/>
-      <x:c r="H88"/>
+      <x:c r="H88" t="str">
+        <x:v>GrantGoldIfCellCount</x:v>
+      </x:c>
       <x:c r="I88"/>
-      <x:c r="J88"/>
-      <x:c r="K88"/>
+      <x:c r="J88" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+      </x:c>
       <x:c r="L88"/>
     </x:row>
     <x:row r="89">
@@ -2687,10 +2705,16 @@
       <x:c r="E89"/>
       <x:c r="F89"/>
       <x:c r="G89"/>
-      <x:c r="H89"/>
+      <x:c r="H89" t="str">
+        <x:v>GrantItemRollIfCellCount</x:v>
+      </x:c>
       <x:c r="I89"/>
-      <x:c r="J89"/>
-      <x:c r="K89"/>
+      <x:c r="J89" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K89" t="str">
+        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+      </x:c>
       <x:c r="L89"/>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad7cb71ccf844c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re0e52a6cf9cb4934"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1149,7 +1149,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>酸：未上菜时场上同菜谱食物倍率×value</x:v>
+        <x:v>酸：结算开始时，未上菜则场上全部食物倍率×value</x:v>
       </x:c>
       <x:c r="L14"/>
     </x:row>
@@ -1162,14 +1162,14 @@
       <x:c r="F15"/>
       <x:c r="G15"/>
       <x:c r="H15" t="str">
-        <x:v>SaltyRecipeGold</x:v>
+        <x:v>SaltyRecipeFlat</x:v>
       </x:c>
       <x:c r="I15"/>
       <x:c r="J15" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>咸：未上菜时场上每个同菜谱食物+value金币</x:v>
+        <x:v>咸：结算开始时，未上菜则场上全部食物基础分+value</x:v>
       </x:c>
       <x:c r="L15"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re0e52a6cf9cb4934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd1a159cbb9a42a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1971,29 +1971,21 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55"/>
-      <x:c r="B55" t="str">
-        <x:v>CompareOp</x:v>
-      </x:c>
-      <x:c r="C55" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D55" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
       <x:c r="E55"/>
-      <x:c r="F55" t="str">
-        <x:v>比较符</x:v>
-      </x:c>
+      <x:c r="F55"/>
       <x:c r="G55"/>
       <x:c r="H55" t="str">
-        <x:v>None</x:v>
+        <x:v>LeftAndSelf</x:v>
       </x:c>
       <x:c r="I55"/>
-      <x:c r="J55" t="str">
-        <x:v>0</x:v>
+      <x:c r="J55" t="n">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>不比较</x:v>
+        <x:v>本菜左侧及自身</x:v>
       </x:c>
       <x:c r="L55"/>
     </x:row>
@@ -2006,14 +1998,14 @@
       <x:c r="F56"/>
       <x:c r="G56"/>
       <x:c r="H56" t="str">
-        <x:v>Gte</x:v>
+        <x:v>UpAndSelf</x:v>
       </x:c>
       <x:c r="I56"/>
-      <x:c r="J56" t="str">
-        <x:v>1</x:v>
+      <x:c r="J56" t="n">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>大于等于</x:v>
+        <x:v>本菜上侧及自身</x:v>
       </x:c>
       <x:c r="L56"/>
     </x:row>
@@ -2026,14 +2018,14 @@
       <x:c r="F57"/>
       <x:c r="G57"/>
       <x:c r="H57" t="str">
-        <x:v>Lte</x:v>
+        <x:v>RightAndSelf</x:v>
       </x:c>
       <x:c r="I57"/>
-      <x:c r="J57" t="str">
-        <x:v>2</x:v>
+      <x:c r="J57" t="n">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>小于等于</x:v>
+        <x:v>本菜右侧及自身</x:v>
       </x:c>
       <x:c r="L57"/>
     </x:row>
@@ -2046,34 +2038,42 @@
       <x:c r="F58"/>
       <x:c r="G58"/>
       <x:c r="H58" t="str">
-        <x:v>Eq</x:v>
+        <x:v>DownAndSelf</x:v>
       </x:c>
       <x:c r="I58"/>
-      <x:c r="J58" t="str">
-        <x:v>3</x:v>
+      <x:c r="J58" t="n">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>等于</x:v>
+        <x:v>本菜下侧及自身</x:v>
       </x:c>
       <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59"/>
-      <x:c r="B59"/>
-      <x:c r="C59"/>
-      <x:c r="D59"/>
+      <x:c r="B59" t="str">
+        <x:v>CompareOp</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E59"/>
-      <x:c r="F59"/>
+      <x:c r="F59" t="str">
+        <x:v>比较符</x:v>
+      </x:c>
       <x:c r="G59"/>
       <x:c r="H59" t="str">
-        <x:v>Gt</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I59"/>
       <x:c r="J59" t="str">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>大于</x:v>
+        <x:v>不比较</x:v>
       </x:c>
       <x:c r="L59"/>
     </x:row>
@@ -2086,42 +2086,34 @@
       <x:c r="F60"/>
       <x:c r="G60"/>
       <x:c r="H60" t="str">
-        <x:v>Lt</x:v>
+        <x:v>Gte</x:v>
       </x:c>
       <x:c r="I60"/>
       <x:c r="J60" t="str">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>小于</x:v>
+        <x:v>大于等于</x:v>
       </x:c>
       <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61"/>
-      <x:c r="B61" t="str">
-        <x:v>CountMode</x:v>
-      </x:c>
-      <x:c r="C61" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D61" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B61"/>
+      <x:c r="C61"/>
+      <x:c r="D61"/>
       <x:c r="E61"/>
-      <x:c r="F61" t="str">
-        <x:v>计数模式</x:v>
-      </x:c>
+      <x:c r="F61"/>
       <x:c r="G61"/>
       <x:c r="H61" t="str">
-        <x:v>Per</x:v>
+        <x:v>Lte</x:v>
       </x:c>
       <x:c r="I61"/>
       <x:c r="J61" t="str">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>每有1个:count=raw</x:v>
+        <x:v>小于等于</x:v>
       </x:c>
       <x:c r="L61"/>
     </x:row>
@@ -2134,14 +2126,14 @@
       <x:c r="F62"/>
       <x:c r="G62"/>
       <x:c r="H62" t="str">
-        <x:v>Reach</x:v>
+        <x:v>Eq</x:v>
       </x:c>
       <x:c r="I62"/>
       <x:c r="J62" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>达到阈值:闸门</x:v>
+        <x:v>等于</x:v>
       </x:c>
       <x:c r="L62"/>
     </x:row>
@@ -2154,90 +2146,82 @@
       <x:c r="F63"/>
       <x:c r="G63"/>
       <x:c r="H63" t="str">
-        <x:v>Gate</x:v>
+        <x:v>Gt</x:v>
       </x:c>
       <x:c r="I63"/>
       <x:c r="J63" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>布尔条件:闸门</x:v>
+        <x:v>大于</x:v>
       </x:c>
       <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64"/>
-      <x:c r="B64" t="str">
-        <x:v>CountUnit</x:v>
-      </x:c>
-      <x:c r="C64" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D64" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
       <x:c r="E64"/>
-      <x:c r="F64" t="str">
-        <x:v>计数单位</x:v>
-      </x:c>
+      <x:c r="F64"/>
       <x:c r="G64"/>
       <x:c r="H64" t="str">
-        <x:v>Instances</x:v>
+        <x:v>Lt</x:v>
       </x:c>
       <x:c r="I64"/>
       <x:c r="J64" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>按实例(个)</x:v>
+        <x:v>小于</x:v>
       </x:c>
       <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65"/>
-      <x:c r="B65"/>
-      <x:c r="C65"/>
-      <x:c r="D65"/>
+      <x:c r="B65" t="str">
+        <x:v>CountMode</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E65"/>
-      <x:c r="F65"/>
+      <x:c r="F65" t="str">
+        <x:v>计数模式</x:v>
+      </x:c>
       <x:c r="G65"/>
       <x:c r="H65" t="str">
-        <x:v>Kinds</x:v>
+        <x:v>Per</x:v>
       </x:c>
       <x:c r="I65"/>
       <x:c r="J65" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>按BaseId去重(种)</x:v>
+        <x:v>每有1个:count=raw</x:v>
       </x:c>
       <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66"/>
-      <x:c r="B66" t="str">
-        <x:v>SkillActionType</x:v>
-      </x:c>
-      <x:c r="C66" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D66" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
       <x:c r="E66"/>
-      <x:c r="F66" t="str">
-        <x:v>技能行为类型</x:v>
-      </x:c>
+      <x:c r="F66"/>
       <x:c r="G66"/>
       <x:c r="H66" t="str">
-        <x:v>None</x:v>
+        <x:v>Reach</x:v>
       </x:c>
       <x:c r="I66"/>
       <x:c r="J66" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>无行为</x:v>
+        <x:v>达到阈值:闸门</x:v>
       </x:c>
       <x:c r="L66"/>
     </x:row>
@@ -2250,34 +2234,42 @@
       <x:c r="F67"/>
       <x:c r="G67"/>
       <x:c r="H67" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>Gate</x:v>
       </x:c>
       <x:c r="I67"/>
       <x:c r="J67" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>目标加法区+X*count</x:v>
+        <x:v>布尔条件:闸门</x:v>
       </x:c>
       <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68"/>
-      <x:c r="B68"/>
-      <x:c r="C68"/>
-      <x:c r="D68"/>
+      <x:c r="B68" t="str">
+        <x:v>CountUnit</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E68"/>
-      <x:c r="F68"/>
+      <x:c r="F68" t="str">
+        <x:v>计数单位</x:v>
+      </x:c>
       <x:c r="G68"/>
       <x:c r="H68" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>Instances</x:v>
       </x:c>
       <x:c r="I68"/>
       <x:c r="J68" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>目标乘区*X(叠count次)</x:v>
+        <x:v>按实例(个)</x:v>
       </x:c>
       <x:c r="L68"/>
     </x:row>
@@ -2290,34 +2282,42 @@
       <x:c r="F69"/>
       <x:c r="G69"/>
       <x:c r="H69" t="str">
-        <x:v>TransferSkills</x:v>
+        <x:v>Kinds</x:v>
       </x:c>
       <x:c r="I69"/>
       <x:c r="J69" t="str">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>来源技能传递给目标</x:v>
+        <x:v>按BaseId去重(种)</x:v>
       </x:c>
       <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70"/>
-      <x:c r="B70"/>
-      <x:c r="C70"/>
-      <x:c r="D70"/>
+      <x:c r="B70" t="str">
+        <x:v>SkillActionType</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E70"/>
-      <x:c r="F70"/>
+      <x:c r="F70" t="str">
+        <x:v>技能行为类型</x:v>
+      </x:c>
       <x:c r="G70"/>
       <x:c r="H70" t="str">
-        <x:v>AddLayer</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I70"/>
       <x:c r="J70" t="str">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>层数+X(mult时*X)</x:v>
+        <x:v>无行为</x:v>
       </x:c>
       <x:c r="L70"/>
     </x:row>
@@ -2330,14 +2330,14 @@
       <x:c r="F71"/>
       <x:c r="G71"/>
       <x:c r="H71" t="str">
-        <x:v>ConsumeLayer</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I71"/>
       <x:c r="J71" t="str">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>层数-X</x:v>
+        <x:v>目标加法区+X*count</x:v>
       </x:c>
       <x:c r="L71"/>
     </x:row>
@@ -2350,14 +2350,14 @@
       <x:c r="F72"/>
       <x:c r="G72"/>
       <x:c r="H72" t="str">
-        <x:v>GrantGold</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I72"/>
       <x:c r="J72" t="str">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>获得X*count金币</x:v>
+        <x:v>目标乘区*X(叠count次)</x:v>
       </x:c>
       <x:c r="L72"/>
     </x:row>
@@ -2370,14 +2370,14 @@
       <x:c r="F73"/>
       <x:c r="G73"/>
       <x:c r="H73" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>TransferSkills</x:v>
       </x:c>
       <x:c r="I73"/>
       <x:c r="J73" t="str">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
+        <x:v>来源技能传递给目标</x:v>
       </x:c>
       <x:c r="L73"/>
     </x:row>
@@ -2390,14 +2390,14 @@
       <x:c r="F74"/>
       <x:c r="G74"/>
       <x:c r="H74" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddLayer</x:v>
       </x:c>
       <x:c r="I74"/>
       <x:c r="J74" t="str">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>目标永久加法+X(跨结算持久)</x:v>
+        <x:v>层数+X(mult时*X)</x:v>
       </x:c>
       <x:c r="L74"/>
     </x:row>
@@ -2410,14 +2410,14 @@
       <x:c r="F75"/>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>AddCountAs</x:v>
+        <x:v>ConsumeLayer</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>目标"视为食物数"+X*count</x:v>
+        <x:v>层数-X</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
@@ -2430,14 +2430,14 @@
       <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>CopySkill</x:v>
+        <x:v>GrantGold</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
+        <x:v>获得X*count金币</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
@@ -2450,14 +2450,14 @@
       <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>TriggerSweetTransfer</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I77"/>
       <x:c r="J77" t="str">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
+        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
@@ -2470,14 +2470,14 @@
       <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>AddCurrentMult</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="str">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
+        <x:v>目标永久加法+X(跨结算持久)</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2490,42 +2490,34 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>AddCurrentScore</x:v>
+        <x:v>AddCountAs</x:v>
       </x:c>
       <x:c r="I79"/>
       <x:c r="J79" t="str">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
+        <x:v>目标"视为食物数"+X*count</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80"/>
-      <x:c r="B80" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C80" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D80" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
       <x:c r="E80"/>
-      <x:c r="F80" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>CopySkill</x:v>
       </x:c>
       <x:c r="I80"/>
       <x:c r="J80" t="str">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>结算时</x:v>
+        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2538,42 +2530,34 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>TriggerSweetTransfer</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="str">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82"/>
-      <x:c r="B82" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C82" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D82" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
       <x:c r="E82"/>
-      <x:c r="F82" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>None</x:v>
+        <x:v>AddCurrentMult</x:v>
       </x:c>
       <x:c r="I82"/>
-      <x:c r="J82" t="n">
-        <x:v>0</x:v>
+      <x:c r="J82" t="str">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>无</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2586,34 +2570,42 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>AddCurrentScore</x:v>
       </x:c>
       <x:c r="I83"/>
-      <x:c r="J83" t="n">
-        <x:v>1</x:v>
+      <x:c r="J83" t="str">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84"/>
-      <x:c r="B84"/>
-      <x:c r="C84"/>
-      <x:c r="D84"/>
+      <x:c r="B84" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E84"/>
-      <x:c r="F84"/>
+      <x:c r="F84" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I84"/>
-      <x:c r="J84" t="n">
-        <x:v>2</x:v>
+      <x:c r="J84" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2626,34 +2618,42 @@
       <x:c r="F85"/>
       <x:c r="G85"/>
       <x:c r="H85" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I85"/>
-      <x:c r="J85" t="n">
-        <x:v>3</x:v>
+      <x:c r="J85" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86"/>
-      <x:c r="B86"/>
-      <x:c r="C86"/>
-      <x:c r="D86"/>
+      <x:c r="B86" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E86"/>
-      <x:c r="F86"/>
+      <x:c r="F86" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G86"/>
       <x:c r="H86" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I86"/>
       <x:c r="J86" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L86"/>
     </x:row>
@@ -2666,14 +2666,14 @@
       <x:c r="F87"/>
       <x:c r="G87"/>
       <x:c r="H87" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I87"/>
       <x:c r="J87" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L87"/>
     </x:row>
@@ -2686,14 +2686,14 @@
       <x:c r="F88"/>
       <x:c r="G88"/>
       <x:c r="H88" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I88"/>
       <x:c r="J88" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L88"/>
     </x:row>
@@ -2706,16 +2706,96 @@
       <x:c r="F89"/>
       <x:c r="G89"/>
       <x:c r="H89" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I89"/>
       <x:c r="J89" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K89" t="str">
+        <x:v>倍率+值(临时,大理石)</x:v>
+      </x:c>
+      <x:c r="L89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90"/>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
+      <x:c r="H90" t="str">
+        <x:v>AddMult</x:v>
+      </x:c>
+      <x:c r="I90"/>
+      <x:c r="J90" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K90" t="str">
+        <x:v>倍率×值(黑曜石)</x:v>
+      </x:c>
+      <x:c r="L90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91"/>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
+      <x:c r="H91" t="str">
+        <x:v>AddMultFlatPerCell</x:v>
+      </x:c>
+      <x:c r="I91"/>
+      <x:c r="J91" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+      </x:c>
+      <x:c r="L91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92"/>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
+      <x:c r="H92" t="str">
+        <x:v>GrantGoldIfCellCount</x:v>
+      </x:c>
+      <x:c r="I92"/>
+      <x:c r="J92" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K92" t="str">
+        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+      </x:c>
+      <x:c r="L92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93"/>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
+      <x:c r="H93" t="str">
+        <x:v>GrantItemRollIfCellCount</x:v>
+      </x:c>
+      <x:c r="I93"/>
+      <x:c r="J93" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K89" t="str">
+      <x:c r="K93" t="str">
         <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
       </x:c>
-      <x:c r="L89"/>
+      <x:c r="L93"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd1a159cbb9a42a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82600dc338bc454d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1109,7 +1109,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>结算优先级层级增量(甜+1/苦-1)，不产生分数效果</x:v>
+        <x:v>结算优先级层级增量(甜 +1/苦 -1)，不产生分数效果</x:v>
       </x:c>
       <x:c r="L12"/>
     </x:row>
@@ -1277,7 +1277,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>作用域内菜数</x:v>
+        <x:v>作用域内食物数量</x:v>
       </x:c>
       <x:c r="L20"/>
     </x:row>
@@ -1297,7 +1297,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>作用域内占格数比较阈值的菜数</x:v>
+        <x:v>作用域内占格数比较阈值的食物数量</x:v>
       </x:c>
       <x:c r="L21"/>
     </x:row>
@@ -1317,7 +1317,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>上菜顺序在前/后的菜数</x:v>
+        <x:v>上菜顺序在前/后的食物数量</x:v>
       </x:c>
       <x:c r="L22"/>
     </x:row>
@@ -1337,7 +1337,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>作用域内同BaseId的菜数</x:v>
+        <x:v>作用域内同BaseId的食物数量</x:v>
       </x:c>
       <x:c r="L23"/>
     </x:row>
@@ -1377,7 +1377,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>本次品鉴本种数量/已结算次数</x:v>
+        <x:v>本场经营挑战本种数量/已结算次数</x:v>
       </x:c>
       <x:c r="L25"/>
     </x:row>
@@ -1417,7 +1417,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>作用域内形状匹配condParam的菜数</x:v>
+        <x:v>作用域内形状匹配condParam的食物数量</x:v>
       </x:c>
       <x:c r="L27"/>
     </x:row>
@@ -1437,7 +1437,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>菜谱内菜数比较阈值(闸门)</x:v>
+        <x:v>食谱内食物数量比较阈值(闸门)</x:v>
       </x:c>
       <x:c r="L28"/>
     </x:row>
@@ -1497,7 +1497,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>作用域内指定分类(condParam)的菜数</x:v>
+        <x:v>作用域内指定分类(condParam)的食物数量</x:v>
       </x:c>
       <x:c r="L31"/>
     </x:row>
@@ -1517,7 +1517,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>作用域内带某行为类技能(condParam)的菜数</x:v>
+        <x:v>作用域内带某行为类技能(condParam)的食物数量</x:v>
       </x:c>
       <x:c r="L32"/>
     </x:row>
@@ -1745,7 +1745,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>菜谱</x:v>
+        <x:v>食谱</x:v>
       </x:c>
       <x:c r="L43"/>
     </x:row>
@@ -2201,7 +2201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>每有1个:count=raw</x:v>
+        <x:v>每有1 个:count=raw</x:v>
       </x:c>
       <x:c r="L65"/>
     </x:row>
@@ -2357,7 +2357,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>目标乘区*X(叠count次)</x:v>
+        <x:v>目标倍率 ×X（叠加 count 次）</x:v>
       </x:c>
       <x:c r="L72"/>
     </x:row>
@@ -2457,7 +2457,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>目标乘区+X*count(加法叠加到倍率)</x:v>
+        <x:v>目标倍率 +X×count（加法叠加到倍率）</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
@@ -2557,7 +2557,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1格食物</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1 格食物</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2577,7 +2577,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>目标分数加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
+        <x:v>目标美味值加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2753,7 +2753,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>每占1格本材质倍率+值(翡翠)</x:v>
+        <x:v>每占1 格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L91"/>
     </x:row>
@@ -2773,7 +2773,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>占&gt;=阈值格获得金币(金)</x:v>
+        <x:v>占≥阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L92"/>
     </x:row>
@@ -2793,7 +2793,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>占&gt;=阈值格1/3获得主动道具(银)</x:v>
+        <x:v>占≥阈值格1/3获得消耗品(银)</x:v>
       </x:c>
       <x:c r="L93"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82600dc338bc454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60617ac425ae44a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2793,7 +2793,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>占≥阈值格1/3获得消耗品(银)</x:v>
+        <x:v>占≥阈值格1/2获得消耗品(银)</x:v>
       </x:c>
       <x:c r="L93"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re958e0b2ff7742b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa50396b1228434c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1082,14 +1082,14 @@
       <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11" t="str">
-        <x:v>GrantGold</x:v>
+        <x:v>ServePriority</x:v>
       </x:c>
       <x:c r="I11"/>
       <x:c r="J11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>结算时获得金币(锈)</x:v>
+        <x:v>鲜：可摆放候选中严格优先出菜，无鲜菜时回退普通候选</x:v>
       </x:c>
       <x:c r="L11"/>
     </x:row>
@@ -1142,14 +1142,14 @@
       <x:c r="F14"/>
       <x:c r="G14"/>
       <x:c r="H14" t="str">
-        <x:v>SourRecipeMult</x:v>
+        <x:v>RecipeAddMultFlat</x:v>
       </x:c>
       <x:c r="I14"/>
       <x:c r="J14" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>酸：结算开始时，未上菜则场上全部食物倍率×value</x:v>
+        <x:v>酸：结算开始时，每层未上菜酸使场上全部食物倍率+值</x:v>
       </x:c>
       <x:c r="L14"/>
     </x:row>
@@ -1162,14 +1162,14 @@
       <x:c r="F15"/>
       <x:c r="G15"/>
       <x:c r="H15" t="str">
-        <x:v>SaltyRecipeFlat</x:v>
+        <x:v>ExtraSettlementChance</x:v>
       </x:c>
       <x:c r="I15"/>
       <x:c r="J15" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>咸：结算开始时，未上菜则场上全部食物基础分+value</x:v>
+        <x:v>咸：每层独立按概率使本菜额外完整结算1次</x:v>
       </x:c>
       <x:c r="L15"/>
     </x:row>
@@ -2877,6 +2877,2036 @@
       </x:c>
       <x:c r="L97"/>
     </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101"/>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+      <x:c r="G101"/>
+      <x:c r="H101"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102"/>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+      <x:c r="G102"/>
+      <x:c r="H102"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
+      <x:c r="H103"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+      <x:c r="G104"/>
+      <x:c r="H104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
+      <x:c r="G105"/>
+      <x:c r="H105"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
+      <x:c r="G109"/>
+      <x:c r="H109"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+      <x:c r="G110"/>
+      <x:c r="H110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+      <x:c r="G111"/>
+      <x:c r="H111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
+      <x:c r="G112"/>
+      <x:c r="H112"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
+      <x:c r="G114"/>
+      <x:c r="H114"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+      <x:c r="G116"/>
+      <x:c r="H116"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118"/>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+      <x:c r="G118"/>
+      <x:c r="H118"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119"/>
+      <x:c r="B119"/>
+      <x:c r="C119"/>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
+      <x:c r="F119"/>
+      <x:c r="G119"/>
+      <x:c r="H119"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120"/>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
+      <x:c r="D120"/>
+      <x:c r="E120"/>
+      <x:c r="F120"/>
+      <x:c r="G120"/>
+      <x:c r="H120"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121"/>
+      <x:c r="B121"/>
+      <x:c r="C121"/>
+      <x:c r="D121"/>
+      <x:c r="E121"/>
+      <x:c r="F121"/>
+      <x:c r="G121"/>
+      <x:c r="H121"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122"/>
+      <x:c r="B122"/>
+      <x:c r="C122"/>
+      <x:c r="D122"/>
+      <x:c r="E122"/>
+      <x:c r="F122"/>
+      <x:c r="G122"/>
+      <x:c r="H122"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123"/>
+      <x:c r="B123"/>
+      <x:c r="C123"/>
+      <x:c r="D123"/>
+      <x:c r="E123"/>
+      <x:c r="F123"/>
+      <x:c r="G123"/>
+      <x:c r="H123"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124"/>
+      <x:c r="B124"/>
+      <x:c r="C124"/>
+      <x:c r="D124"/>
+      <x:c r="E124"/>
+      <x:c r="F124"/>
+      <x:c r="G124"/>
+      <x:c r="H124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125"/>
+      <x:c r="B125"/>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+      <x:c r="F125"/>
+      <x:c r="G125"/>
+      <x:c r="H125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126"/>
+      <x:c r="B126"/>
+      <x:c r="C126"/>
+      <x:c r="D126"/>
+      <x:c r="E126"/>
+      <x:c r="F126"/>
+      <x:c r="G126"/>
+      <x:c r="H126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127"/>
+      <x:c r="B127"/>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127"/>
+      <x:c r="G127"/>
+      <x:c r="H127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128"/>
+      <x:c r="B128"/>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128"/>
+      <x:c r="G128"/>
+      <x:c r="H128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129"/>
+      <x:c r="B129"/>
+      <x:c r="C129"/>
+      <x:c r="D129"/>
+      <x:c r="E129"/>
+      <x:c r="F129"/>
+      <x:c r="G129"/>
+      <x:c r="H129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130"/>
+      <x:c r="B130"/>
+      <x:c r="C130"/>
+      <x:c r="D130"/>
+      <x:c r="E130"/>
+      <x:c r="F130"/>
+      <x:c r="G130"/>
+      <x:c r="H130"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131"/>
+      <x:c r="B131"/>
+      <x:c r="C131"/>
+      <x:c r="D131"/>
+      <x:c r="E131"/>
+      <x:c r="F131"/>
+      <x:c r="G131"/>
+      <x:c r="H131"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132"/>
+      <x:c r="B132"/>
+      <x:c r="C132"/>
+      <x:c r="D132"/>
+      <x:c r="E132"/>
+      <x:c r="F132"/>
+      <x:c r="G132"/>
+      <x:c r="H132"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133"/>
+      <x:c r="B133"/>
+      <x:c r="C133"/>
+      <x:c r="D133"/>
+      <x:c r="E133"/>
+      <x:c r="F133"/>
+      <x:c r="G133"/>
+      <x:c r="H133"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134"/>
+      <x:c r="B134"/>
+      <x:c r="C134"/>
+      <x:c r="D134"/>
+      <x:c r="E134"/>
+      <x:c r="F134"/>
+      <x:c r="G134"/>
+      <x:c r="H134"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135"/>
+      <x:c r="B135"/>
+      <x:c r="C135"/>
+      <x:c r="D135"/>
+      <x:c r="E135"/>
+      <x:c r="F135"/>
+      <x:c r="G135"/>
+      <x:c r="H135"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136"/>
+      <x:c r="B136"/>
+      <x:c r="C136"/>
+      <x:c r="D136"/>
+      <x:c r="E136"/>
+      <x:c r="F136"/>
+      <x:c r="G136"/>
+      <x:c r="H136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137"/>
+      <x:c r="B137"/>
+      <x:c r="C137"/>
+      <x:c r="D137"/>
+      <x:c r="E137"/>
+      <x:c r="F137"/>
+      <x:c r="G137"/>
+      <x:c r="H137"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138"/>
+      <x:c r="B138"/>
+      <x:c r="C138"/>
+      <x:c r="D138"/>
+      <x:c r="E138"/>
+      <x:c r="F138"/>
+      <x:c r="G138"/>
+      <x:c r="H138"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139"/>
+      <x:c r="B139"/>
+      <x:c r="C139"/>
+      <x:c r="D139"/>
+      <x:c r="E139"/>
+      <x:c r="F139"/>
+      <x:c r="G139"/>
+      <x:c r="H139"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140"/>
+      <x:c r="B140"/>
+      <x:c r="C140"/>
+      <x:c r="D140"/>
+      <x:c r="E140"/>
+      <x:c r="F140"/>
+      <x:c r="G140"/>
+      <x:c r="H140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141"/>
+      <x:c r="B141"/>
+      <x:c r="C141"/>
+      <x:c r="D141"/>
+      <x:c r="E141"/>
+      <x:c r="F141"/>
+      <x:c r="G141"/>
+      <x:c r="H141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142"/>
+      <x:c r="B142"/>
+      <x:c r="C142"/>
+      <x:c r="D142"/>
+      <x:c r="E142"/>
+      <x:c r="F142"/>
+      <x:c r="G142"/>
+      <x:c r="H142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143"/>
+      <x:c r="B143"/>
+      <x:c r="C143"/>
+      <x:c r="D143"/>
+      <x:c r="E143"/>
+      <x:c r="F143"/>
+      <x:c r="G143"/>
+      <x:c r="H143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144"/>
+      <x:c r="B144"/>
+      <x:c r="C144"/>
+      <x:c r="D144"/>
+      <x:c r="E144"/>
+      <x:c r="F144"/>
+      <x:c r="G144"/>
+      <x:c r="H144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145"/>
+      <x:c r="B145"/>
+      <x:c r="C145"/>
+      <x:c r="D145"/>
+      <x:c r="E145"/>
+      <x:c r="F145"/>
+      <x:c r="G145"/>
+      <x:c r="H145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146"/>
+      <x:c r="B146"/>
+      <x:c r="C146"/>
+      <x:c r="D146"/>
+      <x:c r="E146"/>
+      <x:c r="F146"/>
+      <x:c r="G146"/>
+      <x:c r="H146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147"/>
+      <x:c r="B147"/>
+      <x:c r="C147"/>
+      <x:c r="D147"/>
+      <x:c r="E147"/>
+      <x:c r="F147"/>
+      <x:c r="G147"/>
+      <x:c r="H147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148"/>
+      <x:c r="B148"/>
+      <x:c r="C148"/>
+      <x:c r="D148"/>
+      <x:c r="E148"/>
+      <x:c r="F148"/>
+      <x:c r="G148"/>
+      <x:c r="H148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149"/>
+      <x:c r="B149"/>
+      <x:c r="C149"/>
+      <x:c r="D149"/>
+      <x:c r="E149"/>
+      <x:c r="F149"/>
+      <x:c r="G149"/>
+      <x:c r="H149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150"/>
+      <x:c r="B150"/>
+      <x:c r="C150"/>
+      <x:c r="D150"/>
+      <x:c r="E150"/>
+      <x:c r="F150"/>
+      <x:c r="G150"/>
+      <x:c r="H150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151"/>
+      <x:c r="B151"/>
+      <x:c r="C151"/>
+      <x:c r="D151"/>
+      <x:c r="E151"/>
+      <x:c r="F151"/>
+      <x:c r="G151"/>
+      <x:c r="H151"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152"/>
+      <x:c r="B152"/>
+      <x:c r="C152"/>
+      <x:c r="D152"/>
+      <x:c r="E152"/>
+      <x:c r="F152"/>
+      <x:c r="G152"/>
+      <x:c r="H152"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153"/>
+      <x:c r="B153"/>
+      <x:c r="C153"/>
+      <x:c r="D153"/>
+      <x:c r="E153"/>
+      <x:c r="F153"/>
+      <x:c r="G153"/>
+      <x:c r="H153"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154"/>
+      <x:c r="B154"/>
+      <x:c r="C154"/>
+      <x:c r="D154"/>
+      <x:c r="E154"/>
+      <x:c r="F154"/>
+      <x:c r="G154"/>
+      <x:c r="H154"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155"/>
+      <x:c r="B155"/>
+      <x:c r="C155"/>
+      <x:c r="D155"/>
+      <x:c r="E155"/>
+      <x:c r="F155"/>
+      <x:c r="G155"/>
+      <x:c r="H155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156"/>
+      <x:c r="B156"/>
+      <x:c r="C156"/>
+      <x:c r="D156"/>
+      <x:c r="E156"/>
+      <x:c r="F156"/>
+      <x:c r="G156"/>
+      <x:c r="H156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157"/>
+      <x:c r="B157"/>
+      <x:c r="C157"/>
+      <x:c r="D157"/>
+      <x:c r="E157"/>
+      <x:c r="F157"/>
+      <x:c r="G157"/>
+      <x:c r="H157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158"/>
+      <x:c r="B158"/>
+      <x:c r="C158"/>
+      <x:c r="D158"/>
+      <x:c r="E158"/>
+      <x:c r="F158"/>
+      <x:c r="G158"/>
+      <x:c r="H158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159"/>
+      <x:c r="B159"/>
+      <x:c r="C159"/>
+      <x:c r="D159"/>
+      <x:c r="E159"/>
+      <x:c r="F159"/>
+      <x:c r="G159"/>
+      <x:c r="H159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160"/>
+      <x:c r="B160"/>
+      <x:c r="C160"/>
+      <x:c r="D160"/>
+      <x:c r="E160"/>
+      <x:c r="F160"/>
+      <x:c r="G160"/>
+      <x:c r="H160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161"/>
+      <x:c r="B161"/>
+      <x:c r="C161"/>
+      <x:c r="D161"/>
+      <x:c r="E161"/>
+      <x:c r="F161"/>
+      <x:c r="G161"/>
+      <x:c r="H161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162"/>
+      <x:c r="B162"/>
+      <x:c r="C162"/>
+      <x:c r="D162"/>
+      <x:c r="E162"/>
+      <x:c r="F162"/>
+      <x:c r="G162"/>
+      <x:c r="H162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163"/>
+      <x:c r="B163"/>
+      <x:c r="C163"/>
+      <x:c r="D163"/>
+      <x:c r="E163"/>
+      <x:c r="F163"/>
+      <x:c r="G163"/>
+      <x:c r="H163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164"/>
+      <x:c r="B164"/>
+      <x:c r="C164"/>
+      <x:c r="D164"/>
+      <x:c r="E164"/>
+      <x:c r="F164"/>
+      <x:c r="G164"/>
+      <x:c r="H164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165"/>
+      <x:c r="B165"/>
+      <x:c r="C165"/>
+      <x:c r="D165"/>
+      <x:c r="E165"/>
+      <x:c r="F165"/>
+      <x:c r="G165"/>
+      <x:c r="H165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166"/>
+      <x:c r="B166"/>
+      <x:c r="C166"/>
+      <x:c r="D166"/>
+      <x:c r="E166"/>
+      <x:c r="F166"/>
+      <x:c r="G166"/>
+      <x:c r="H166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167"/>
+      <x:c r="B167"/>
+      <x:c r="C167"/>
+      <x:c r="D167"/>
+      <x:c r="E167"/>
+      <x:c r="F167"/>
+      <x:c r="G167"/>
+      <x:c r="H167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168"/>
+      <x:c r="B168"/>
+      <x:c r="C168"/>
+      <x:c r="D168"/>
+      <x:c r="E168"/>
+      <x:c r="F168"/>
+      <x:c r="G168"/>
+      <x:c r="H168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169"/>
+      <x:c r="B169"/>
+      <x:c r="C169"/>
+      <x:c r="D169"/>
+      <x:c r="E169"/>
+      <x:c r="F169"/>
+      <x:c r="G169"/>
+      <x:c r="H169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170"/>
+      <x:c r="B170"/>
+      <x:c r="C170"/>
+      <x:c r="D170"/>
+      <x:c r="E170"/>
+      <x:c r="F170"/>
+      <x:c r="G170"/>
+      <x:c r="H170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171"/>
+      <x:c r="B171"/>
+      <x:c r="C171"/>
+      <x:c r="D171"/>
+      <x:c r="E171"/>
+      <x:c r="F171"/>
+      <x:c r="G171"/>
+      <x:c r="H171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172"/>
+      <x:c r="B172"/>
+      <x:c r="C172"/>
+      <x:c r="D172"/>
+      <x:c r="E172"/>
+      <x:c r="F172"/>
+      <x:c r="G172"/>
+      <x:c r="H172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173"/>
+      <x:c r="B173"/>
+      <x:c r="C173"/>
+      <x:c r="D173"/>
+      <x:c r="E173"/>
+      <x:c r="F173"/>
+      <x:c r="G173"/>
+      <x:c r="H173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174"/>
+      <x:c r="B174"/>
+      <x:c r="C174"/>
+      <x:c r="D174"/>
+      <x:c r="E174"/>
+      <x:c r="F174"/>
+      <x:c r="G174"/>
+      <x:c r="H174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175"/>
+      <x:c r="B175"/>
+      <x:c r="C175"/>
+      <x:c r="D175"/>
+      <x:c r="E175"/>
+      <x:c r="F175"/>
+      <x:c r="G175"/>
+      <x:c r="H175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176"/>
+      <x:c r="B176"/>
+      <x:c r="C176"/>
+      <x:c r="D176"/>
+      <x:c r="E176"/>
+      <x:c r="F176"/>
+      <x:c r="G176"/>
+      <x:c r="H176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177"/>
+      <x:c r="B177"/>
+      <x:c r="C177"/>
+      <x:c r="D177"/>
+      <x:c r="E177"/>
+      <x:c r="F177"/>
+      <x:c r="G177"/>
+      <x:c r="H177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178"/>
+      <x:c r="B178"/>
+      <x:c r="C178"/>
+      <x:c r="D178"/>
+      <x:c r="E178"/>
+      <x:c r="F178"/>
+      <x:c r="G178"/>
+      <x:c r="H178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179"/>
+      <x:c r="B179"/>
+      <x:c r="C179"/>
+      <x:c r="D179"/>
+      <x:c r="E179"/>
+      <x:c r="F179"/>
+      <x:c r="G179"/>
+      <x:c r="H179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180"/>
+      <x:c r="B180"/>
+      <x:c r="C180"/>
+      <x:c r="D180"/>
+      <x:c r="E180"/>
+      <x:c r="F180"/>
+      <x:c r="G180"/>
+      <x:c r="H180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181"/>
+      <x:c r="B181"/>
+      <x:c r="C181"/>
+      <x:c r="D181"/>
+      <x:c r="E181"/>
+      <x:c r="F181"/>
+      <x:c r="G181"/>
+      <x:c r="H181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182"/>
+      <x:c r="B182"/>
+      <x:c r="C182"/>
+      <x:c r="D182"/>
+      <x:c r="E182"/>
+      <x:c r="F182"/>
+      <x:c r="G182"/>
+      <x:c r="H182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183"/>
+      <x:c r="B183"/>
+      <x:c r="C183"/>
+      <x:c r="D183"/>
+      <x:c r="E183"/>
+      <x:c r="F183"/>
+      <x:c r="G183"/>
+      <x:c r="H183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184"/>
+      <x:c r="B184"/>
+      <x:c r="C184"/>
+      <x:c r="D184"/>
+      <x:c r="E184"/>
+      <x:c r="F184"/>
+      <x:c r="G184"/>
+      <x:c r="H184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185"/>
+      <x:c r="B185"/>
+      <x:c r="C185"/>
+      <x:c r="D185"/>
+      <x:c r="E185"/>
+      <x:c r="F185"/>
+      <x:c r="G185"/>
+      <x:c r="H185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186"/>
+      <x:c r="B186"/>
+      <x:c r="C186"/>
+      <x:c r="D186"/>
+      <x:c r="E186"/>
+      <x:c r="F186"/>
+      <x:c r="G186"/>
+      <x:c r="H186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187"/>
+      <x:c r="B187"/>
+      <x:c r="C187"/>
+      <x:c r="D187"/>
+      <x:c r="E187"/>
+      <x:c r="F187"/>
+      <x:c r="G187"/>
+      <x:c r="H187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188"/>
+      <x:c r="B188"/>
+      <x:c r="C188"/>
+      <x:c r="D188"/>
+      <x:c r="E188"/>
+      <x:c r="F188"/>
+      <x:c r="G188"/>
+      <x:c r="H188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189"/>
+      <x:c r="B189"/>
+      <x:c r="C189"/>
+      <x:c r="D189"/>
+      <x:c r="E189"/>
+      <x:c r="F189"/>
+      <x:c r="G189"/>
+      <x:c r="H189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190"/>
+      <x:c r="B190"/>
+      <x:c r="C190"/>
+      <x:c r="D190"/>
+      <x:c r="E190"/>
+      <x:c r="F190"/>
+      <x:c r="G190"/>
+      <x:c r="H190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191"/>
+      <x:c r="B191"/>
+      <x:c r="C191"/>
+      <x:c r="D191"/>
+      <x:c r="E191"/>
+      <x:c r="F191"/>
+      <x:c r="G191"/>
+      <x:c r="H191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192"/>
+      <x:c r="B192"/>
+      <x:c r="C192"/>
+      <x:c r="D192"/>
+      <x:c r="E192"/>
+      <x:c r="F192"/>
+      <x:c r="G192"/>
+      <x:c r="H192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193"/>
+      <x:c r="B193"/>
+      <x:c r="C193"/>
+      <x:c r="D193"/>
+      <x:c r="E193"/>
+      <x:c r="F193"/>
+      <x:c r="G193"/>
+      <x:c r="H193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194"/>
+      <x:c r="B194"/>
+      <x:c r="C194"/>
+      <x:c r="D194"/>
+      <x:c r="E194"/>
+      <x:c r="F194"/>
+      <x:c r="G194"/>
+      <x:c r="H194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195"/>
+      <x:c r="B195"/>
+      <x:c r="C195"/>
+      <x:c r="D195"/>
+      <x:c r="E195"/>
+      <x:c r="F195"/>
+      <x:c r="G195"/>
+      <x:c r="H195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196"/>
+      <x:c r="B196"/>
+      <x:c r="C196"/>
+      <x:c r="D196"/>
+      <x:c r="E196"/>
+      <x:c r="F196"/>
+      <x:c r="G196"/>
+      <x:c r="H196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197"/>
+      <x:c r="B197"/>
+      <x:c r="C197"/>
+      <x:c r="D197"/>
+      <x:c r="E197"/>
+      <x:c r="F197"/>
+      <x:c r="G197"/>
+      <x:c r="H197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198"/>
+      <x:c r="B198"/>
+      <x:c r="C198"/>
+      <x:c r="D198"/>
+      <x:c r="E198"/>
+      <x:c r="F198"/>
+      <x:c r="G198"/>
+      <x:c r="H198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199"/>
+      <x:c r="B199"/>
+      <x:c r="C199"/>
+      <x:c r="D199"/>
+      <x:c r="E199"/>
+      <x:c r="F199"/>
+      <x:c r="G199"/>
+      <x:c r="H199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200"/>
+      <x:c r="B200"/>
+      <x:c r="C200"/>
+      <x:c r="D200"/>
+      <x:c r="E200"/>
+      <x:c r="F200"/>
+      <x:c r="G200"/>
+      <x:c r="H200"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201"/>
+      <x:c r="B201"/>
+      <x:c r="C201"/>
+      <x:c r="D201"/>
+      <x:c r="E201"/>
+      <x:c r="F201"/>
+      <x:c r="G201"/>
+      <x:c r="H201"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202"/>
+      <x:c r="B202"/>
+      <x:c r="C202"/>
+      <x:c r="D202"/>
+      <x:c r="E202"/>
+      <x:c r="F202"/>
+      <x:c r="G202"/>
+      <x:c r="H202"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203"/>
+      <x:c r="B203"/>
+      <x:c r="C203"/>
+      <x:c r="D203"/>
+      <x:c r="E203"/>
+      <x:c r="F203"/>
+      <x:c r="G203"/>
+      <x:c r="H203"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204"/>
+      <x:c r="B204"/>
+      <x:c r="C204"/>
+      <x:c r="D204"/>
+      <x:c r="E204"/>
+      <x:c r="F204"/>
+      <x:c r="G204"/>
+      <x:c r="H204"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205"/>
+      <x:c r="B205"/>
+      <x:c r="C205"/>
+      <x:c r="D205"/>
+      <x:c r="E205"/>
+      <x:c r="F205"/>
+      <x:c r="G205"/>
+      <x:c r="H205"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206"/>
+      <x:c r="B206"/>
+      <x:c r="C206"/>
+      <x:c r="D206"/>
+      <x:c r="E206"/>
+      <x:c r="F206"/>
+      <x:c r="G206"/>
+      <x:c r="H206"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207"/>
+      <x:c r="B207"/>
+      <x:c r="C207"/>
+      <x:c r="D207"/>
+      <x:c r="E207"/>
+      <x:c r="F207"/>
+      <x:c r="G207"/>
+      <x:c r="H207"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208"/>
+      <x:c r="B208"/>
+      <x:c r="C208"/>
+      <x:c r="D208"/>
+      <x:c r="E208"/>
+      <x:c r="F208"/>
+      <x:c r="G208"/>
+      <x:c r="H208"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209"/>
+      <x:c r="B209"/>
+      <x:c r="C209"/>
+      <x:c r="D209"/>
+      <x:c r="E209"/>
+      <x:c r="F209"/>
+      <x:c r="G209"/>
+      <x:c r="H209"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210"/>
+      <x:c r="B210"/>
+      <x:c r="C210"/>
+      <x:c r="D210"/>
+      <x:c r="E210"/>
+      <x:c r="F210"/>
+      <x:c r="G210"/>
+      <x:c r="H210"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211"/>
+      <x:c r="B211"/>
+      <x:c r="C211"/>
+      <x:c r="D211"/>
+      <x:c r="E211"/>
+      <x:c r="F211"/>
+      <x:c r="G211"/>
+      <x:c r="H211"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212"/>
+      <x:c r="B212"/>
+      <x:c r="C212"/>
+      <x:c r="D212"/>
+      <x:c r="E212"/>
+      <x:c r="F212"/>
+      <x:c r="G212"/>
+      <x:c r="H212"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213"/>
+      <x:c r="B213"/>
+      <x:c r="C213"/>
+      <x:c r="D213"/>
+      <x:c r="E213"/>
+      <x:c r="F213"/>
+      <x:c r="G213"/>
+      <x:c r="H213"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214"/>
+      <x:c r="B214"/>
+      <x:c r="C214"/>
+      <x:c r="D214"/>
+      <x:c r="E214"/>
+      <x:c r="F214"/>
+      <x:c r="G214"/>
+      <x:c r="H214"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215"/>
+      <x:c r="B215"/>
+      <x:c r="C215"/>
+      <x:c r="D215"/>
+      <x:c r="E215"/>
+      <x:c r="F215"/>
+      <x:c r="G215"/>
+      <x:c r="H215"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216"/>
+      <x:c r="B216"/>
+      <x:c r="C216"/>
+      <x:c r="D216"/>
+      <x:c r="E216"/>
+      <x:c r="F216"/>
+      <x:c r="G216"/>
+      <x:c r="H216"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217"/>
+      <x:c r="B217"/>
+      <x:c r="C217"/>
+      <x:c r="D217"/>
+      <x:c r="E217"/>
+      <x:c r="F217"/>
+      <x:c r="G217"/>
+      <x:c r="H217"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218"/>
+      <x:c r="B218"/>
+      <x:c r="C218"/>
+      <x:c r="D218"/>
+      <x:c r="E218"/>
+      <x:c r="F218"/>
+      <x:c r="G218"/>
+      <x:c r="H218"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219"/>
+      <x:c r="B219"/>
+      <x:c r="C219"/>
+      <x:c r="D219"/>
+      <x:c r="E219"/>
+      <x:c r="F219"/>
+      <x:c r="G219"/>
+      <x:c r="H219"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220"/>
+      <x:c r="B220"/>
+      <x:c r="C220"/>
+      <x:c r="D220"/>
+      <x:c r="E220"/>
+      <x:c r="F220"/>
+      <x:c r="G220"/>
+      <x:c r="H220"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221"/>
+      <x:c r="B221"/>
+      <x:c r="C221"/>
+      <x:c r="D221"/>
+      <x:c r="E221"/>
+      <x:c r="F221"/>
+      <x:c r="G221"/>
+      <x:c r="H221"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222"/>
+      <x:c r="B222"/>
+      <x:c r="C222"/>
+      <x:c r="D222"/>
+      <x:c r="E222"/>
+      <x:c r="F222"/>
+      <x:c r="G222"/>
+      <x:c r="H222"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223"/>
+      <x:c r="B223"/>
+      <x:c r="C223"/>
+      <x:c r="D223"/>
+      <x:c r="E223"/>
+      <x:c r="F223"/>
+      <x:c r="G223"/>
+      <x:c r="H223"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224"/>
+      <x:c r="B224"/>
+      <x:c r="C224"/>
+      <x:c r="D224"/>
+      <x:c r="E224"/>
+      <x:c r="F224"/>
+      <x:c r="G224"/>
+      <x:c r="H224"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225"/>
+      <x:c r="B225"/>
+      <x:c r="C225"/>
+      <x:c r="D225"/>
+      <x:c r="E225"/>
+      <x:c r="F225"/>
+      <x:c r="G225"/>
+      <x:c r="H225"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226"/>
+      <x:c r="B226"/>
+      <x:c r="C226"/>
+      <x:c r="D226"/>
+      <x:c r="E226"/>
+      <x:c r="F226"/>
+      <x:c r="G226"/>
+      <x:c r="H226"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227"/>
+      <x:c r="B227"/>
+      <x:c r="C227"/>
+      <x:c r="D227"/>
+      <x:c r="E227"/>
+      <x:c r="F227"/>
+      <x:c r="G227"/>
+      <x:c r="H227"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228"/>
+      <x:c r="B228"/>
+      <x:c r="C228"/>
+      <x:c r="D228"/>
+      <x:c r="E228"/>
+      <x:c r="F228"/>
+      <x:c r="G228"/>
+      <x:c r="H228"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229"/>
+      <x:c r="B229"/>
+      <x:c r="C229"/>
+      <x:c r="D229"/>
+      <x:c r="E229"/>
+      <x:c r="F229"/>
+      <x:c r="G229"/>
+      <x:c r="H229"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230"/>
+      <x:c r="B230"/>
+      <x:c r="C230"/>
+      <x:c r="D230"/>
+      <x:c r="E230"/>
+      <x:c r="F230"/>
+      <x:c r="G230"/>
+      <x:c r="H230"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231"/>
+      <x:c r="B231"/>
+      <x:c r="C231"/>
+      <x:c r="D231"/>
+      <x:c r="E231"/>
+      <x:c r="F231"/>
+      <x:c r="G231"/>
+      <x:c r="H231"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232"/>
+      <x:c r="B232"/>
+      <x:c r="C232"/>
+      <x:c r="D232"/>
+      <x:c r="E232"/>
+      <x:c r="F232"/>
+      <x:c r="G232"/>
+      <x:c r="H232"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233"/>
+      <x:c r="B233"/>
+      <x:c r="C233"/>
+      <x:c r="D233"/>
+      <x:c r="E233"/>
+      <x:c r="F233"/>
+      <x:c r="G233"/>
+      <x:c r="H233"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234"/>
+      <x:c r="B234"/>
+      <x:c r="C234"/>
+      <x:c r="D234"/>
+      <x:c r="E234"/>
+      <x:c r="F234"/>
+      <x:c r="G234"/>
+      <x:c r="H234"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235"/>
+      <x:c r="B235"/>
+      <x:c r="C235"/>
+      <x:c r="D235"/>
+      <x:c r="E235"/>
+      <x:c r="F235"/>
+      <x:c r="G235"/>
+      <x:c r="H235"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236"/>
+      <x:c r="B236"/>
+      <x:c r="C236"/>
+      <x:c r="D236"/>
+      <x:c r="E236"/>
+      <x:c r="F236"/>
+      <x:c r="G236"/>
+      <x:c r="H236"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237"/>
+      <x:c r="B237"/>
+      <x:c r="C237"/>
+      <x:c r="D237"/>
+      <x:c r="E237"/>
+      <x:c r="F237"/>
+      <x:c r="G237"/>
+      <x:c r="H237"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238"/>
+      <x:c r="B238"/>
+      <x:c r="C238"/>
+      <x:c r="D238"/>
+      <x:c r="E238"/>
+      <x:c r="F238"/>
+      <x:c r="G238"/>
+      <x:c r="H238"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239"/>
+      <x:c r="B239"/>
+      <x:c r="C239"/>
+      <x:c r="D239"/>
+      <x:c r="E239"/>
+      <x:c r="F239"/>
+      <x:c r="G239"/>
+      <x:c r="H239"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240"/>
+      <x:c r="B240"/>
+      <x:c r="C240"/>
+      <x:c r="D240"/>
+      <x:c r="E240"/>
+      <x:c r="F240"/>
+      <x:c r="G240"/>
+      <x:c r="H240"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241"/>
+      <x:c r="B241"/>
+      <x:c r="C241"/>
+      <x:c r="D241"/>
+      <x:c r="E241"/>
+      <x:c r="F241"/>
+      <x:c r="G241"/>
+      <x:c r="H241"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242"/>
+      <x:c r="B242"/>
+      <x:c r="C242"/>
+      <x:c r="D242"/>
+      <x:c r="E242"/>
+      <x:c r="F242"/>
+      <x:c r="G242"/>
+      <x:c r="H242"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243"/>
+      <x:c r="B243"/>
+      <x:c r="C243"/>
+      <x:c r="D243"/>
+      <x:c r="E243"/>
+      <x:c r="F243"/>
+      <x:c r="G243"/>
+      <x:c r="H243"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244"/>
+      <x:c r="B244"/>
+      <x:c r="C244"/>
+      <x:c r="D244"/>
+      <x:c r="E244"/>
+      <x:c r="F244"/>
+      <x:c r="G244"/>
+      <x:c r="H244"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245"/>
+      <x:c r="B245"/>
+      <x:c r="C245"/>
+      <x:c r="D245"/>
+      <x:c r="E245"/>
+      <x:c r="F245"/>
+      <x:c r="G245"/>
+      <x:c r="H245"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246"/>
+      <x:c r="B246"/>
+      <x:c r="C246"/>
+      <x:c r="D246"/>
+      <x:c r="E246"/>
+      <x:c r="F246"/>
+      <x:c r="G246"/>
+      <x:c r="H246"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247"/>
+      <x:c r="B247"/>
+      <x:c r="C247"/>
+      <x:c r="D247"/>
+      <x:c r="E247"/>
+      <x:c r="F247"/>
+      <x:c r="G247"/>
+      <x:c r="H247"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248"/>
+      <x:c r="B248"/>
+      <x:c r="C248"/>
+      <x:c r="D248"/>
+      <x:c r="E248"/>
+      <x:c r="F248"/>
+      <x:c r="G248"/>
+      <x:c r="H248"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249"/>
+      <x:c r="B249"/>
+      <x:c r="C249"/>
+      <x:c r="D249"/>
+      <x:c r="E249"/>
+      <x:c r="F249"/>
+      <x:c r="G249"/>
+      <x:c r="H249"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250"/>
+      <x:c r="B250"/>
+      <x:c r="C250"/>
+      <x:c r="D250"/>
+      <x:c r="E250"/>
+      <x:c r="F250"/>
+      <x:c r="G250"/>
+      <x:c r="H250"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251"/>
+      <x:c r="B251"/>
+      <x:c r="C251"/>
+      <x:c r="D251"/>
+      <x:c r="E251"/>
+      <x:c r="F251"/>
+      <x:c r="G251"/>
+      <x:c r="H251"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252"/>
+      <x:c r="B252"/>
+      <x:c r="C252"/>
+      <x:c r="D252"/>
+      <x:c r="E252"/>
+      <x:c r="F252"/>
+      <x:c r="G252"/>
+      <x:c r="H252"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253"/>
+      <x:c r="B253"/>
+      <x:c r="C253"/>
+      <x:c r="D253"/>
+      <x:c r="E253"/>
+      <x:c r="F253"/>
+      <x:c r="G253"/>
+      <x:c r="H253"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254"/>
+      <x:c r="B254"/>
+      <x:c r="C254"/>
+      <x:c r="D254"/>
+      <x:c r="E254"/>
+      <x:c r="F254"/>
+      <x:c r="G254"/>
+      <x:c r="H254"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255"/>
+      <x:c r="B255"/>
+      <x:c r="C255"/>
+      <x:c r="D255"/>
+      <x:c r="E255"/>
+      <x:c r="F255"/>
+      <x:c r="G255"/>
+      <x:c r="H255"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256"/>
+      <x:c r="B256"/>
+      <x:c r="C256"/>
+      <x:c r="D256"/>
+      <x:c r="E256"/>
+      <x:c r="F256"/>
+      <x:c r="G256"/>
+      <x:c r="H256"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257"/>
+      <x:c r="B257"/>
+      <x:c r="C257"/>
+      <x:c r="D257"/>
+      <x:c r="E257"/>
+      <x:c r="F257"/>
+      <x:c r="G257"/>
+      <x:c r="H257"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258"/>
+      <x:c r="B258"/>
+      <x:c r="C258"/>
+      <x:c r="D258"/>
+      <x:c r="E258"/>
+      <x:c r="F258"/>
+      <x:c r="G258"/>
+      <x:c r="H258"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259"/>
+      <x:c r="B259"/>
+      <x:c r="C259"/>
+      <x:c r="D259"/>
+      <x:c r="E259"/>
+      <x:c r="F259"/>
+      <x:c r="G259"/>
+      <x:c r="H259"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260"/>
+      <x:c r="B260"/>
+      <x:c r="C260"/>
+      <x:c r="D260"/>
+      <x:c r="E260"/>
+      <x:c r="F260"/>
+      <x:c r="G260"/>
+      <x:c r="H260"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261"/>
+      <x:c r="B261"/>
+      <x:c r="C261"/>
+      <x:c r="D261"/>
+      <x:c r="E261"/>
+      <x:c r="F261"/>
+      <x:c r="G261"/>
+      <x:c r="H261"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262"/>
+      <x:c r="B262"/>
+      <x:c r="C262"/>
+      <x:c r="D262"/>
+      <x:c r="E262"/>
+      <x:c r="F262"/>
+      <x:c r="G262"/>
+      <x:c r="H262"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263"/>
+      <x:c r="B263"/>
+      <x:c r="C263"/>
+      <x:c r="D263"/>
+      <x:c r="E263"/>
+      <x:c r="F263"/>
+      <x:c r="G263"/>
+      <x:c r="H263"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264"/>
+      <x:c r="B264"/>
+      <x:c r="C264"/>
+      <x:c r="D264"/>
+      <x:c r="E264"/>
+      <x:c r="F264"/>
+      <x:c r="G264"/>
+      <x:c r="H264"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265"/>
+      <x:c r="B265"/>
+      <x:c r="C265"/>
+      <x:c r="D265"/>
+      <x:c r="E265"/>
+      <x:c r="F265"/>
+      <x:c r="G265"/>
+      <x:c r="H265"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266"/>
+      <x:c r="B266"/>
+      <x:c r="C266"/>
+      <x:c r="D266"/>
+      <x:c r="E266"/>
+      <x:c r="F266"/>
+      <x:c r="G266"/>
+      <x:c r="H266"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267"/>
+      <x:c r="B267"/>
+      <x:c r="C267"/>
+      <x:c r="D267"/>
+      <x:c r="E267"/>
+      <x:c r="F267"/>
+      <x:c r="G267"/>
+      <x:c r="H267"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268"/>
+      <x:c r="B268"/>
+      <x:c r="C268"/>
+      <x:c r="D268"/>
+      <x:c r="E268"/>
+      <x:c r="F268"/>
+      <x:c r="G268"/>
+      <x:c r="H268"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269"/>
+      <x:c r="B269"/>
+      <x:c r="C269"/>
+      <x:c r="D269"/>
+      <x:c r="E269"/>
+      <x:c r="F269"/>
+      <x:c r="G269"/>
+      <x:c r="H269"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270"/>
+      <x:c r="B270"/>
+      <x:c r="C270"/>
+      <x:c r="D270"/>
+      <x:c r="E270"/>
+      <x:c r="F270"/>
+      <x:c r="G270"/>
+      <x:c r="H270"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271"/>
+      <x:c r="B271"/>
+      <x:c r="C271"/>
+      <x:c r="D271"/>
+      <x:c r="E271"/>
+      <x:c r="F271"/>
+      <x:c r="G271"/>
+      <x:c r="H271"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272"/>
+      <x:c r="B272"/>
+      <x:c r="C272"/>
+      <x:c r="D272"/>
+      <x:c r="E272"/>
+      <x:c r="F272"/>
+      <x:c r="G272"/>
+      <x:c r="H272"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273"/>
+      <x:c r="B273"/>
+      <x:c r="C273"/>
+      <x:c r="D273"/>
+      <x:c r="E273"/>
+      <x:c r="F273"/>
+      <x:c r="G273"/>
+      <x:c r="H273"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274"/>
+      <x:c r="B274"/>
+      <x:c r="C274"/>
+      <x:c r="D274"/>
+      <x:c r="E274"/>
+      <x:c r="F274"/>
+      <x:c r="G274"/>
+      <x:c r="H274"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275"/>
+      <x:c r="B275"/>
+      <x:c r="C275"/>
+      <x:c r="D275"/>
+      <x:c r="E275"/>
+      <x:c r="F275"/>
+      <x:c r="G275"/>
+      <x:c r="H275"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276"/>
+      <x:c r="B276"/>
+      <x:c r="C276"/>
+      <x:c r="D276"/>
+      <x:c r="E276"/>
+      <x:c r="F276"/>
+      <x:c r="G276"/>
+      <x:c r="H276"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277"/>
+      <x:c r="B277"/>
+      <x:c r="C277"/>
+      <x:c r="D277"/>
+      <x:c r="E277"/>
+      <x:c r="F277"/>
+      <x:c r="G277"/>
+      <x:c r="H277"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278"/>
+      <x:c r="B278"/>
+      <x:c r="C278"/>
+      <x:c r="D278"/>
+      <x:c r="E278"/>
+      <x:c r="F278"/>
+      <x:c r="G278"/>
+      <x:c r="H278"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279"/>
+      <x:c r="B279"/>
+      <x:c r="C279"/>
+      <x:c r="D279"/>
+      <x:c r="E279"/>
+      <x:c r="F279"/>
+      <x:c r="G279"/>
+      <x:c r="H279"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280"/>
+      <x:c r="B280"/>
+      <x:c r="C280"/>
+      <x:c r="D280"/>
+      <x:c r="E280"/>
+      <x:c r="F280"/>
+      <x:c r="G280"/>
+      <x:c r="H280"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281"/>
+      <x:c r="B281"/>
+      <x:c r="C281"/>
+      <x:c r="D281"/>
+      <x:c r="E281"/>
+      <x:c r="F281"/>
+      <x:c r="G281"/>
+      <x:c r="H281"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282"/>
+      <x:c r="B282"/>
+      <x:c r="C282"/>
+      <x:c r="D282"/>
+      <x:c r="E282"/>
+      <x:c r="F282"/>
+      <x:c r="G282"/>
+      <x:c r="H282"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283"/>
+      <x:c r="B283"/>
+      <x:c r="C283"/>
+      <x:c r="D283"/>
+      <x:c r="E283"/>
+      <x:c r="F283"/>
+      <x:c r="G283"/>
+      <x:c r="H283"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284"/>
+      <x:c r="B284"/>
+      <x:c r="C284"/>
+      <x:c r="D284"/>
+      <x:c r="E284"/>
+      <x:c r="F284"/>
+      <x:c r="G284"/>
+      <x:c r="H284"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285"/>
+      <x:c r="B285"/>
+      <x:c r="C285"/>
+      <x:c r="D285"/>
+      <x:c r="E285"/>
+      <x:c r="F285"/>
+      <x:c r="G285"/>
+      <x:c r="H285"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286"/>
+      <x:c r="B286"/>
+      <x:c r="C286"/>
+      <x:c r="D286"/>
+      <x:c r="E286"/>
+      <x:c r="F286"/>
+      <x:c r="G286"/>
+      <x:c r="H286"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287"/>
+      <x:c r="B287"/>
+      <x:c r="C287"/>
+      <x:c r="D287"/>
+      <x:c r="E287"/>
+      <x:c r="F287"/>
+      <x:c r="G287"/>
+      <x:c r="H287"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288"/>
+      <x:c r="B288"/>
+      <x:c r="C288"/>
+      <x:c r="D288"/>
+      <x:c r="E288"/>
+      <x:c r="F288"/>
+      <x:c r="G288"/>
+      <x:c r="H288"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289"/>
+      <x:c r="B289"/>
+      <x:c r="C289"/>
+      <x:c r="D289"/>
+      <x:c r="E289"/>
+      <x:c r="F289"/>
+      <x:c r="G289"/>
+      <x:c r="H289"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290"/>
+      <x:c r="B290"/>
+      <x:c r="C290"/>
+      <x:c r="D290"/>
+      <x:c r="E290"/>
+      <x:c r="F290"/>
+      <x:c r="G290"/>
+      <x:c r="H290"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291"/>
+      <x:c r="B291"/>
+      <x:c r="C291"/>
+      <x:c r="D291"/>
+      <x:c r="E291"/>
+      <x:c r="F291"/>
+      <x:c r="G291"/>
+      <x:c r="H291"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292"/>
+      <x:c r="B292"/>
+      <x:c r="C292"/>
+      <x:c r="D292"/>
+      <x:c r="E292"/>
+      <x:c r="F292"/>
+      <x:c r="G292"/>
+      <x:c r="H292"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293"/>
+      <x:c r="B293"/>
+      <x:c r="C293"/>
+      <x:c r="D293"/>
+      <x:c r="E293"/>
+      <x:c r="F293"/>
+      <x:c r="G293"/>
+      <x:c r="H293"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294"/>
+      <x:c r="B294"/>
+      <x:c r="C294"/>
+      <x:c r="D294"/>
+      <x:c r="E294"/>
+      <x:c r="F294"/>
+      <x:c r="G294"/>
+      <x:c r="H294"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295"/>
+      <x:c r="B295"/>
+      <x:c r="C295"/>
+      <x:c r="D295"/>
+      <x:c r="E295"/>
+      <x:c r="F295"/>
+      <x:c r="G295"/>
+      <x:c r="H295"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296"/>
+      <x:c r="B296"/>
+      <x:c r="C296"/>
+      <x:c r="D296"/>
+      <x:c r="E296"/>
+      <x:c r="F296"/>
+      <x:c r="G296"/>
+      <x:c r="H296"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297"/>
+      <x:c r="B297"/>
+      <x:c r="C297"/>
+      <x:c r="D297"/>
+      <x:c r="E297"/>
+      <x:c r="F297"/>
+      <x:c r="G297"/>
+      <x:c r="H297"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298"/>
+      <x:c r="B298"/>
+      <x:c r="C298"/>
+      <x:c r="D298"/>
+      <x:c r="E298"/>
+      <x:c r="F298"/>
+      <x:c r="G298"/>
+      <x:c r="H298"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299"/>
+      <x:c r="B299"/>
+      <x:c r="C299"/>
+      <x:c r="D299"/>
+      <x:c r="E299"/>
+      <x:c r="F299"/>
+      <x:c r="G299"/>
+      <x:c r="H299"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300"/>
+      <x:c r="B300"/>
+      <x:c r="C300"/>
+      <x:c r="D300"/>
+      <x:c r="E300"/>
+      <x:c r="F300"/>
+      <x:c r="G300"/>
+      <x:c r="H300"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_gameplay.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8043176b78184d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fa1c92c3b3a45dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2051,49 +2051,49 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59"/>
-      <x:c r="B59" t="str">
-        <x:v>CompareOp</x:v>
-      </x:c>
-      <x:c r="C59" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D59" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
       <x:c r="E59"/>
-      <x:c r="F59" t="str">
-        <x:v>比较符</x:v>
-      </x:c>
+      <x:c r="F59"/>
       <x:c r="G59"/>
       <x:c r="H59" t="str">
-        <x:v>None</x:v>
+        <x:v>RowAndColumn</x:v>
       </x:c>
       <x:c r="I59"/>
-      <x:c r="J59" t="str">
-        <x:v>0</x:v>
+      <x:c r="J59" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>不比较</x:v>
+        <x:v>同行及同列（不含自身）</x:v>
       </x:c>
       <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60"/>
-      <x:c r="B60"/>
-      <x:c r="C60"/>
-      <x:c r="D60"/>
+      <x:c r="B60" t="str">
+        <x:v>CompareOp</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E60"/>
-      <x:c r="F60"/>
+      <x:c r="F60" t="str">
+        <x:v>比较符</x:v>
+      </x:c>
       <x:c r="G60"/>
       <x:c r="H60" t="str">
-        <x:v>Gte</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I60"/>
       <x:c r="J60" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>大于等于</x:v>
+        <x:v>不比较</x:v>
       </x:c>
       <x:c r="L60"/>
     </x:row>
@@ -2106,14 +2106,14 @@
       <x:c r="F61"/>
       <x:c r="G61"/>
       <x:c r="H61" t="str">
-        <x:v>Lte</x:v>
+        <x:v>Gte</x:v>
       </x:c>
       <x:c r="I61"/>
       <x:c r="J61" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>小于等于</x:v>
+        <x:v>大于等于</x:v>
       </x:c>
       <x:c r="L61"/>
     </x:row>
@@ -2126,14 +2126,14 @@
       <x:c r="F62"/>
       <x:c r="G62"/>
       <x:c r="H62" t="str">
-        <x:v>Eq</x:v>
+        <x:v>Lte</x:v>
       </x:c>
       <x:c r="I62"/>
       <x:c r="J62" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>等于</x:v>
+        <x:v>小于等于</x:v>
       </x:c>
       <x:c r="L62"/>
     </x:row>
@@ -2146,14 +2146,14 @@
       <x:c r="F63"/>
       <x:c r="G63"/>
       <x:c r="H63" t="str">
-        <x:v>Gt</x:v>
+        <x:v>Eq</x:v>
       </x:c>
       <x:c r="I63"/>
       <x:c r="J63" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>大于</x:v>
+        <x:v>等于</x:v>
       </x:c>
       <x:c r="L63"/>
     </x:row>
@@ -2166,62 +2166,62 @@
       <x:c r="F64"/>
       <x:c r="G64"/>
       <x:c r="H64" t="str">
-        <x:v>Lt</x:v>
+        <x:v>Gt</x:v>
       </x:c>
       <x:c r="I64"/>
       <x:c r="J64" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>小于</x:v>
+        <x:v>大于</x:v>
       </x:c>
       <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65"/>
-      <x:c r="B65" t="str">
-        <x:v>CountMode</x:v>
-      </x:c>
-      <x:c r="C65" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D65" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
       <x:c r="E65"/>
-      <x:c r="F65" t="str">
-        <x:v>计数模式</x:v>
-      </x:c>
+      <x:c r="F65"/>
       <x:c r="G65"/>
       <x:c r="H65" t="str">
-        <x:v>Per</x:v>
+        <x:v>Lt</x:v>
       </x:c>
       <x:c r="I65"/>
       <x:c r="J65" t="str">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>每有1 个:count=raw</x:v>
+        <x:v>小于</x:v>
       </x:c>
       <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66"/>
-      <x:c r="B66"/>
-      <x:c r="C66"/>
-      <x:c r="D66"/>
+      <x:c r="B66" t="str">
+        <x:v>CountMode</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E66"/>
-      <x:c r="F66"/>
+      <x:c r="F66" t="str">
+        <x:v>计数模式</x:v>
+      </x:c>
       <x:c r="G66"/>
       <x:c r="H66" t="str">
-        <x:v>Reach</x:v>
+        <x:v>Per</x:v>
       </x:c>
       <x:c r="I66"/>
       <x:c r="J66" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>达到阈值:闸门</x:v>
+        <x:v>每有1 个:count=raw</x:v>
       </x:c>
       <x:c r="L66"/>
     </x:row>
@@ -2234,62 +2234,62 @@
       <x:c r="F67"/>
       <x:c r="G67"/>
       <x:c r="H67" t="str">
-        <x:v>Gate</x:v>
+        <x:v>Reach</x:v>
       </x:c>
       <x:c r="I67"/>
       <x:c r="J67" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>布尔条件:闸门</x:v>
+        <x:v>达到阈值:闸门</x:v>
       </x:c>
       <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68"/>
-      <x:c r="B68" t="str">
-        <x:v>CountUnit</x:v>
-      </x:c>
-      <x:c r="C68" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D68" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
       <x:c r="E68"/>
-      <x:c r="F68" t="str">
-        <x:v>计数单位</x:v>
-      </x:c>
+      <x:c r="F68"/>
       <x:c r="G68"/>
       <x:c r="H68" t="str">
-        <x:v>Instances</x:v>
+        <x:v>Gate</x:v>
       </x:c>
       <x:c r="I68"/>
       <x:c r="J68" t="str">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>按有效份数</x:v>
+        <x:v>布尔条件:闸门</x:v>
       </x:c>
       <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69"/>
-      <x:c r="B69"/>
-      <x:c r="C69"/>
-      <x:c r="D69"/>
+      <x:c r="B69" t="str">
+        <x:v>CountUnit</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E69"/>
-      <x:c r="F69"/>
+      <x:c r="F69" t="str">
+        <x:v>计数单位</x:v>
+      </x:c>
       <x:c r="G69"/>
       <x:c r="H69" t="str">
-        <x:v>Kinds</x:v>
+        <x:v>Instances</x:v>
       </x:c>
       <x:c r="I69"/>
       <x:c r="J69" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>按BaseId去重(种)</x:v>
+        <x:v>按有效份数</x:v>
       </x:c>
       <x:c r="L69"/>
     </x:row>
@@ -2302,62 +2302,62 @@
       <x:c r="F70"/>
       <x:c r="G70"/>
       <x:c r="H70" t="str">
-        <x:v>PhysicalInstances</x:v>
+        <x:v>Kinds</x:v>
       </x:c>
       <x:c r="I70"/>
-      <x:c r="J70" t="n">
-        <x:v>2</x:v>
+      <x:c r="J70" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>按物理食物数(个)</x:v>
+        <x:v>按BaseId去重(种)</x:v>
       </x:c>
       <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71"/>
-      <x:c r="B71" t="str">
-        <x:v>SkillActionType</x:v>
-      </x:c>
-      <x:c r="C71" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D71" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
       <x:c r="E71"/>
-      <x:c r="F71" t="str">
-        <x:v>技能行为类型</x:v>
-      </x:c>
+      <x:c r="F71"/>
       <x:c r="G71"/>
       <x:c r="H71" t="str">
-        <x:v>None</x:v>
+        <x:v>PhysicalInstances</x:v>
       </x:c>
       <x:c r="I71"/>
-      <x:c r="J71" t="str">
-        <x:v>0</x:v>
+      <x:c r="J71" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>无行为</x:v>
+        <x:v>按物理食物数(个)</x:v>
       </x:c>
       <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72"/>
-      <x:c r="B72"/>
-      <x:c r="C72"/>
-      <x:c r="D72"/>
+      <x:c r="B72" t="str">
+        <x:v>SkillActionType</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E72"/>
-      <x:c r="F72"/>
+      <x:c r="F72" t="str">
+        <x:v>技能行为类型</x:v>
+      </x:c>
       <x:c r="G72"/>
       <x:c r="H72" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I72"/>
       <x:c r="J72" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>目标加法区+X*count</x:v>
+        <x:v>无行为</x:v>
       </x:c>
       <x:c r="L72"/>
     </x:row>
@@ -2370,14 +2370,14 @@
       <x:c r="F73"/>
       <x:c r="G73"/>
       <x:c r="H73" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I73"/>
       <x:c r="J73" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>目标倍率 ×X（叠加 count 次）</x:v>
+        <x:v>目标加法区+X*count</x:v>
       </x:c>
       <x:c r="L73"/>
     </x:row>
@@ -2390,14 +2390,14 @@
       <x:c r="F74"/>
       <x:c r="G74"/>
       <x:c r="H74" t="str">
-        <x:v>TransferSkills</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I74"/>
       <x:c r="J74" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>来源技能传递给目标</x:v>
+        <x:v>目标倍率 ×X（叠加 count 次）</x:v>
       </x:c>
       <x:c r="L74"/>
     </x:row>
@@ -2410,14 +2410,14 @@
       <x:c r="F75"/>
       <x:c r="G75"/>
       <x:c r="H75" t="str">
-        <x:v>AddLayer</x:v>
+        <x:v>TransferSkills</x:v>
       </x:c>
       <x:c r="I75"/>
       <x:c r="J75" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>层数+X(mult时*X)</x:v>
+        <x:v>来源技能传递给目标</x:v>
       </x:c>
       <x:c r="L75"/>
     </x:row>
@@ -2430,14 +2430,14 @@
       <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>ConsumeLayer</x:v>
+        <x:v>AddLayer</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="str">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>层数-X</x:v>
+        <x:v>层数+X(mult时*X)</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
@@ -2450,14 +2450,14 @@
       <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>GrantGold</x:v>
+        <x:v>ConsumeLayer</x:v>
       </x:c>
       <x:c r="I77"/>
       <x:c r="J77" t="str">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>获得X*count金币</x:v>
+        <x:v>层数-X</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
@@ -2470,14 +2470,14 @@
       <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>GrantGold</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="str">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>目标倍率 +X×count（加法叠加到倍率）</x:v>
+        <x:v>获得X*count金币</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2490,14 +2490,14 @@
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I79"/>
       <x:c r="J79" t="str">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>目标永久加法+X(跨结算持久)</x:v>
+        <x:v>目标倍率 +X×count（加法叠加到倍率）</x:v>
       </x:c>
       <x:c r="L79"/>
     </x:row>
@@ -2510,14 +2510,14 @@
       <x:c r="F80"/>
       <x:c r="G80"/>
       <x:c r="H80" t="str">
-        <x:v>AddCountAs</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I80"/>
       <x:c r="J80" t="str">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>目标有效份数+X*count</x:v>
+        <x:v>目标永久加法+X(跨结算持久)</x:v>
       </x:c>
       <x:c r="L80"/>
     </x:row>
@@ -2530,14 +2530,14 @@
       <x:c r="F81"/>
       <x:c r="G81"/>
       <x:c r="H81" t="str">
-        <x:v>CopySkill</x:v>
+        <x:v>AddCountAs</x:v>
       </x:c>
       <x:c r="I81"/>
       <x:c r="J81" t="str">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
+        <x:v>目标有效份数+X*count</x:v>
       </x:c>
       <x:c r="L81"/>
     </x:row>
@@ -2550,14 +2550,14 @@
       <x:c r="F82"/>
       <x:c r="G82"/>
       <x:c r="H82" t="str">
-        <x:v>TriggerSweetTransfer</x:v>
+        <x:v>CopySkill</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="str">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
+        <x:v>从来源作用域随机复制actionCount个技能给目标</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2570,14 +2570,14 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>AddCurrentMult</x:v>
+        <x:v>TriggerSweetTransfer</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="str">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1 格食物</x:v>
+        <x:v>触发作用域内食物各执行一次自身甜蜜传递</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2590,14 +2590,14 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>AddCurrentScore</x:v>
+        <x:v>AddCurrentMult</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="str">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>目标美味值加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
+        <x:v>目标倍率加上来源当前倍率之和；默认来源自身，source:one-cell时来源为所有实际占1 格食物</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
@@ -2610,14 +2610,14 @@
       <x:c r="F85"/>
       <x:c r="G85"/>
       <x:c r="H85" t="str">
-        <x:v>RequestRecipeRemoval</x:v>
+        <x:v>AddCurrentScore</x:v>
       </x:c>
       <x:c r="I85"/>
-      <x:c r="J85" t="n">
-        <x:v>19</x:v>
+      <x:c r="J85" t="str">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>登记营业成败判定后的食谱移除请求</x:v>
+        <x:v>目标美味值加上自身当前分数（基础分+固定加分，不含倍率）</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
@@ -2630,14 +2630,14 @@
       <x:c r="F86"/>
       <x:c r="G86"/>
       <x:c r="H86" t="str">
-        <x:v>AddEmptyCountAs</x:v>
+        <x:v>RequestRecipeRemoval</x:v>
       </x:c>
       <x:c r="I86"/>
       <x:c r="J86" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>当前结算每个空格提供X份；同类效果相加</x:v>
+        <x:v>登记营业成败判定后的食谱移除请求</x:v>
       </x:c>
       <x:c r="L86"/>
     </x:row>
@@ -2650,110 +2650,110 @@
       <x:c r="F87"/>
       <x:c r="G87"/>
       <x:c r="H87" t="str">
-        <x:v>AddTemporaryCategory</x:v>
+        <x:v>AddEmptyCountAs</x:v>
       </x:c>
       <x:c r="I87"/>
       <x:c r="J87" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>目标在本场临时增加指定分类</x:v>
+        <x:v>当前结算每个空格提供X份；同类效果相加</x:v>
       </x:c>
       <x:c r="L87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88"/>
-      <x:c r="B88" t="str">
-        <x:v>SkillTrigger</x:v>
-      </x:c>
-      <x:c r="C88" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D88" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
       <x:c r="E88"/>
-      <x:c r="F88" t="str">
-        <x:v>技能触发时机</x:v>
-      </x:c>
+      <x:c r="F88"/>
       <x:c r="G88"/>
       <x:c r="H88" t="str">
-        <x:v>OnSettle</x:v>
+        <x:v>AddTemporaryCategory</x:v>
       </x:c>
       <x:c r="I88"/>
-      <x:c r="J88" t="str">
-        <x:v>0</x:v>
+      <x:c r="J88" t="n">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>结算时</x:v>
+        <x:v>目标在本场临时增加指定分类</x:v>
       </x:c>
       <x:c r="L88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89"/>
-      <x:c r="B89"/>
-      <x:c r="C89"/>
-      <x:c r="D89"/>
+      <x:c r="B89" t="str">
+        <x:v>SkillTrigger</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E89"/>
-      <x:c r="F89"/>
+      <x:c r="F89" t="str">
+        <x:v>技能触发时机</x:v>
+      </x:c>
       <x:c r="G89"/>
       <x:c r="H89" t="str">
-        <x:v>OnServe</x:v>
+        <x:v>OnSettle</x:v>
       </x:c>
       <x:c r="I89"/>
       <x:c r="J89" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>上菜时</x:v>
+        <x:v>结算时</x:v>
       </x:c>
       <x:c r="L89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90"/>
-      <x:c r="B90" t="str">
-        <x:v>MaterialEffectType</x:v>
-      </x:c>
-      <x:c r="C90" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D90" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
       <x:c r="E90"/>
-      <x:c r="F90" t="str">
-        <x:v>餐桌材质效果类型</x:v>
-      </x:c>
+      <x:c r="F90"/>
       <x:c r="G90"/>
       <x:c r="H90" t="str">
-        <x:v>None</x:v>
+        <x:v>OnServe</x:v>
       </x:c>
       <x:c r="I90"/>
-      <x:c r="J90" t="n">
-        <x:v>0</x:v>
+      <x:c r="J90" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>无</x:v>
+        <x:v>上菜时</x:v>
       </x:c>
       <x:c r="L90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91"/>
-      <x:c r="B91"/>
-      <x:c r="C91"/>
-      <x:c r="D91"/>
+      <x:c r="B91" t="str">
+        <x:v>MaterialEffectType</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E91"/>
-      <x:c r="F91"/>
+      <x:c r="F91" t="str">
+        <x:v>餐桌材质效果类型</x:v>
+      </x:c>
       <x:c r="G91"/>
       <x:c r="H91" t="str">
-        <x:v>AddFlat</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="I91"/>
       <x:c r="J91" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>分数+值(临时,樱桃木)</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="L91"/>
     </x:row>
@@ -2766,14 +2766,14 @@
       <x:c r="F92"/>
       <x:c r="G92"/>
       <x:c r="H92" t="str">
-        <x:v>PermanentAddFlat</x:v>
+        <x:v>AddFlat</x:v>
       </x:c>
       <x:c r="I92"/>
       <x:c r="J92" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>分数永久+值(胡桃木)</x:v>
+        <x:v>分数+值(临时,樱桃木)</x:v>
       </x:c>
       <x:c r="L92"/>
     </x:row>
@@ -2786,14 +2786,14 @@
       <x:c r="F93"/>
       <x:c r="G93"/>
       <x:c r="H93" t="str">
-        <x:v>AddMultFlat</x:v>
+        <x:v>PermanentAddFlat</x:v>
       </x:c>
       <x:c r="I93"/>
       <x:c r="J93" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>倍率+值(临时,大理石)</x:v>
+        <x:v>分数永久+值(胡桃木)</x:v>
       </x:c>
       <x:c r="L93"/>
     </x:row>
@@ -2806,14 +2806,14 @@
       <x:c r="F94"/>
       <x:c r="G94"/>
       <x:c r="H94" t="str">
-        <x:v>AddMult</x:v>
+        <x:v>AddMultFlat</x:v>
       </x:c>
       <x:c r="I94"/>
       <x:c r="J94" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>倍率×值(黑曜石)</x:v>
+        <x:v>倍率+值(临时,大理石)</x:v>
       </x:c>
       <x:c r="L94"/>
     </x:row>
@@ -2826,14 +2826,14 @@
       <x:c r="F95"/>
       <x:c r="G95"/>
       <x:c r="H95" t="str">
-        <x:v>AddMultFlatPerCell</x:v>
+        <x:v>AddMult</x:v>
       </x:c>
       <x:c r="I95"/>
       <x:c r="J95" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>每占1 格本材质倍率+值(翡翠)</x:v>
+        <x:v>倍率×值(黑曜石)</x:v>
       </x:c>
       <x:c r="L95"/>
     </x:row>
@@ -2846,14 +2846,14 @@
       <x:c r="F96"/>
       <x:c r="G96"/>
       <x:c r="H96" t="str">
-        <x:v>GrantGoldIfCellCount</x:v>
+        <x:v>AddMultFlatPerCell</x:v>
       </x:c>
       <x:c r="I96"/>
       <x:c r="J96" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>占≥阈值格获得金币(金)</x:v>
+        <x:v>每占1 格本材质倍率+值(翡翠)</x:v>
       </x:c>
       <x:c r="L96"/>
     </x:row>
@@ -2866,14 +2866,14 @@
       <x:c r="F97"/>
       <x:c r="G97"/>
       <x:c r="H97" t="str">
-        <x:v>GrantItemRollIfCellCount</x:v>
+        <x:v>GrantGoldIfCellCount</x:v>
       </x:c>
       <x:c r="I97"/>
       <x:c r="J97" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>每占1格独立1/5获得消耗品(银)</x:v>
+        <x:v>占≥阈值格获得金币(金)</x:v>
       </x:c>
       <x:c r="L97"/>
     </x:row>
@@ -2885,7 +2885,17 @@
       <x:c r="E98"/>
       <x:c r="F98"/>
       <x:c r="G98"/>
-      <x:c r="H98"/>
+      <x:c r="H98" t="str">
+        <x:v>GrantItemRollIfCellCount</x:v>
+      </x:c>
+      <x:c r="I98"/>
+      <x:c r="J98" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>每占1格独立1/5获得消耗品(银)</x:v>
+      </x:c>
+      <x:c r="L98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99"/>
